--- a/Inputs/Canada_LNG_Data_Inputs.xlsx
+++ b/Inputs/Canada_LNG_Data_Inputs.xlsx
@@ -492,7 +492,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29 13:20 UTC</t>
+          <t>2026-08-20 10:00 UTC</t>
         </is>
       </c>
     </row>
@@ -751,19 +751,19 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Methane leakage rate, GWP horizon and electrification. Each is a specific assumption a reader can examine and dispute.</t>
+          <t>Methane leakage rate and GWP horizon. Electrification is no longer a scenario lever: electric drive is not assumed. Each remaining choice is a specific assumption a reader can examine and dispute.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Liquefaction is set per project</t>
+          <t>Liquefaction is a single central value</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>No single central value applies. The factor follows the plant's power source as recorded in the asset register: about 0.29 tCO2e per tonne for gas turbine drive, 0.12 to 0.16 for electric drive. The published figures of 0.16, 0.29 and 0.36 describe different plant configurations rather than competing estimates of one quantity.</t>
+          <t>The liquefaction stage carries a central factor of 0.29 tCO2e per tonne (gas turbine) for every terminal and its whole operating life. 0.12 is kept as range_low and applies only if electrification is contracted and delivered. Electric drive is not assumed for any project.</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>Set by drive type</t>
+          <t>Gas turbine for every terminal</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>gas_turbine uses 0.29 tCO2e per tonne, implied by LNG Canada's environmental assessment. electric_committed and electric_planned use 0.12. The classification is recorded per project in the asset register.</t>
+          <t>Parameter liquefaction_electrification_assumed = none. The register records liquefaction_drive as gas_turbine for all export and bunkering assets. Previous electric_committed and electric_planned classifications are retained in liquefaction_drive_note. Only Cedar and Woodfibre have interconnection works under construction; the remainder rest on MOUs or aspirations conditional on transmission that has not been built.</t>
         </is>
       </c>
     </row>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Gas is chilled to minus 162 degrees at the terminal until it becomes liquid. Energy intensive, and the factor depends entirely on whether the compressors run on gas turbines or grid electricity.</t>
+          <t>Gas is chilled to minus 162 degrees at the terminal until it becomes liquid. Energy intensive. The central factor is gas-turbine drive for every terminal; electric-drive 0.12 is retained only as range_low.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1238,7 +1238,9 @@
           <t>tCO2e per t LNG</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>0.29</v>
+      </c>
       <c r="F4" t="n">
         <v>0.12</v>
       </c>
@@ -1247,17 +1249,17 @@
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>Set per project from the register's power_source field rather than a single value. Gas turbine drive uses 0.29, implied by LNG Canada's own environmental assessment. Electric drive uses 0.12 to 0.16.</t>
+          <t>Gas turbine drive, 0.29 tCO2e per tonne LNG, implied by LNG Canada's environmental assessment of roughly 4 MtCO2e per year against 14 mtpa of capacity. Applied to every terminal for its whole operating life. Electric drive is not assumed for any project.</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>British Columbia legislates a benchmark of 0.16 tCO2e per tonne LNG covering gas entering the facility to loading onto ships, under the Greenhouse Gas Industrial Reporting and Control Act. Global average for LNG plants is about 0.36. Woodfibre claims 0.059 with electric drive. Pacific NorthWest LNG was federally conditioned at 0.21 to 0.22.</t>
+          <t>range_low 0.12 is the electric-drive factor (Pembina Institute electrified LNG scenario). It applies only if electrification is contracted and delivered. It is not used in the central case. range_high 0.36 remains the literature upper bound for gas-turbine plants. British Columbia legislates a benchmark of 0.16 tCO2e per tonne LNG covering gas entering the facility to loading onto ships, under the Greenhouse Gas Industrial Reporting and Control Act.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>The three published figures describe different plant configurations rather than competing estimates of one thing. Facilities above the BC benchmark must buy offsets or pay into a technology fund, so 0.36 should not apply to a compliant BC facility.</t>
+          <t>Whether any proposed terminal will actually run on electric drive. Only Cedar and Woodfibre have interconnection works under construction; the rest rest on MOUs or aspirations conditional on transmission that does not exist. A commitment contingent on infrastructure that does not exist is not a basis for lowering the factor.</t>
         </is>
       </c>
     </row>
@@ -1411,7 +1413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H60"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1531,7 +1533,6 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
@@ -1563,7 +1564,6 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -1595,7 +1595,6 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
@@ -1667,7 +1666,6 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>About 25 per cent below the 40 year case</t>
@@ -1779,7 +1777,6 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1811,7 +1808,6 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1843,7 +1839,6 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1915,7 +1910,6 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
@@ -1947,7 +1941,6 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
@@ -1979,7 +1972,6 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
@@ -2083,7 +2075,6 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
@@ -2115,7 +2106,6 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" s="4" t="inlineStr">
         <is>
           <t>No external citation identified</t>
@@ -2491,7 +2481,6 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
@@ -2523,7 +2512,6 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
@@ -2555,7 +2543,6 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
@@ -2745,10 +2732,9 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Export projects must carry an explicit liquefaction_drive</t>
+          <t>Fallback only for domestic plants that still carry not_published. Export and bunkering assets are recorded as gas_turbine. Electric drive is not assumed for any terminal.</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2807,6 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" s="4" t="inlineStr">
         <is>
           <t>Also required for the per-kWh energy source comparison</t>
@@ -3020,7 +3005,7 @@
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>Exceeds the BC benchmark of 0.16</t>
+          <t>Equals Emission Factors liquefaction central. Applied to every terminal for its whole operating life as of August 2026.</t>
         </is>
       </c>
     </row>
@@ -3053,10 +3038,9 @@
           <t>https://www.pembina.org/</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Below the BC benchmark of 0.16</t>
+          <t>Retained for reference. Not used in the central case. Matches Emission Factors range_low; applies only if electrification is contracted and delivered.</t>
         </is>
       </c>
     </row>
@@ -3169,7 +3153,6 @@
           <t>https://www.bv.com/en-US/perspectives/geographic-location-magnifies-advantages-for-north-american-lng-exports</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
       <c r="H48" s="4" t="inlineStr">
         <is>
           <t>One way</t>
@@ -3593,7 +3576,6 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
       <c r="H59" s="4" t="inlineStr">
         <is>
           <t>Sensitivity worth testing</t>
@@ -3629,8 +3611,49 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
       <c r="H60" s="4" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>liquefaction_electrification_assumed</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>assumption</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Model assumption - no external source</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Electric drive is not assumed for any terminal. Of the projects claiming electrification, only Cedar and Woodfibre have interconnection works under construction; the remainder rest on memoranda of understanding, aspirations conditional on transmission that has not been built, or statements with no firm date. Ksi Lisims holds an MOU with BC Hydro for up to 600 MW conditional on the North Coast Transmission Line expansion, which is not built. LNG Canada Phase 2 states an intention to transition to electric motors as more renewable power becomes available, with no date and no contracted supply. There is not sufficient evidence that electric drive will be in use at these facilities, and a commitment contingent on infrastructure that does not exist is not a basis for lowering the emissions factor. Where electrification is later contracted and built, this assumption should be revisited.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:H60"/>
@@ -3693,9 +3716,6 @@
           <t>CAPACITY TRACKS</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" s="4" t="inlineStr"/>
       <c r="F2" s="4" t="inlineStr"/>
     </row>
@@ -3812,10 +3832,6 @@
       <c r="F6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" s="4" t="inlineStr"/>
       <c r="F7" s="4" t="inlineStr"/>
     </row>
@@ -3825,9 +3841,6 @@
           <t>LIFESPAN SENSITIVITY</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="inlineStr"/>
     </row>
@@ -3847,7 +3860,6 @@
           <t>40 yr for the four main projects</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Default. Not a model assumption.</t>
@@ -3871,7 +3883,6 @@
           <t>30 yr</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Matches Summit Lake's stated operating life. About 25% below default.</t>
@@ -3895,7 +3906,6 @@
           <t>50 yr</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" s="4" t="inlineStr">
         <is>
           <t>CER may issue LNG licences up to 50 years.</t>
@@ -3904,10 +3914,6 @@
       <c r="F11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" s="4" t="inlineStr"/>
       <c r="F12" s="4" t="inlineStr"/>
     </row>
@@ -3917,9 +3923,6 @@
           <t>UPSTREAM AND GWP SCENARIOS</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" s="4" t="inlineStr"/>
       <c r="F13" s="4" t="inlineStr"/>
     </row>
@@ -4340,13 +4343,11 @@
           <t>not applicable</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>not applicable</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="O3" s="4" t="inlineStr">
         <is>
           <t>0.90 mtpa (Tilbury Phase 1a and 1b)</t>
@@ -4424,7 +4425,6 @@
           <t>not applicable</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" s="4" t="inlineStr">
         <is>
           <t>0.32 mtpa (Tilbury Original, Energir, Mt Hayes, Tamaska)</t>
@@ -4472,25 +4472,21 @@
           <t>not applicable</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>not applicable</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>not applicable</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>not applicable</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" s="4" t="inlineStr">
         <is>
           <t>7.50 mtpa nameplate at Saint John, running at about 2.5 per cent</t>
@@ -4729,7 +4725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4868,6 +4864,38 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>liquefaction_electrification_assumed</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>All liquefaction</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Electric drive is not assumed. Revisit if Cedar, Woodfibre or others have electrification contracted and built.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Executed interconnection and contracted renewable supply at a named terminal.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>high - would lower liquefaction by about 80 percent if applied to the whole slate</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Inputs/Canada_LNG_Data_Inputs.xlsx
+++ b/Inputs/Canada_LNG_Data_Inputs.xlsx
@@ -1413,7 +1413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2419,7 +2419,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -2433,99 +2433,117 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>IPCC AR6 WGIII Table SPM.2, remaining budget from 1 Jan 2020 for 50% chance of 1.5C</t>
+          <t>Global Carbon Budget 2025 (Friedlingstein et al., Earth Syst. Sci. Data). Remaining budget from the start of 2026, 50% likelihood. 1.5C.</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>https://www.ipcc.ch/report/ar6/wg3/</t>
+          <t>https://essd.copernicus.org/articles/18/3211/2026/</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2022 vintage</t>
+          <t>2025 (from 1 Jan 2026)</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>CO2 only, declines each year</t>
+          <t>Budget is CO2. Register emissions are GWP100 CO2e. The comparison is CO2e against a CO2 budget and is an approximation; a true CO2-only total is not derivable from this model.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>coal_plant_reference_mw</t>
+          <t>remaining_17c_budget</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>500</v>
+        <v>525</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MW</t>
+          <t>GtCO2</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>assumption</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>Comparator assumption</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="H30" s="4" t="inlineStr"/>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Global Carbon Budget 2025 (Friedlingstein et al., Earth Syst. Sci. Data). Remaining budget from the start of 2026, 50% likelihood. 1.7C.</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://essd.copernicus.org/articles/18/3211/2026/</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2025 (from 1 Jan 2026)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Budget is CO2. Register emissions are GWP100 CO2e. The comparison is CO2e against a CO2 budget and is an approximation; a true CO2-only total is not derivable from this model.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>coal_plant_capacity_factor</t>
+          <t>remaining_2c_budget</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.55</v>
+        <v>1055</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>GtCO2</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>assumption</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Comparator assumption</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr"/>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Global Carbon Budget 2025 (Friedlingstein et al., Earth Syst. Sci. Data). Remaining budget from the start of 2026, 50% likelihood. 2.0C.</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://essd.copernicus.org/articles/18/3211/2026/</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2025 (from 1 Jan 2026)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Budget is CO2. Register emissions are GWP100 CO2e. The comparison is CO2e against a CO2 budget and is an approximation; a true CO2-only total is not derivable from this model.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>coal_tco2e_per_mwh</t>
+          <t>coal_plant_reference_mw</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.95</v>
+        <v>500</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>tCO2e/MWh</t>
+          <t>MW</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2548,35 +2566,30 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>tmx_total_system_bpd</t>
+          <t>coal_plant_capacity_factor</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>890000</v>
+        <v>0.55</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>barrels per day</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>assumption</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Trans Mountain system capacity after the May 2024 expansion</t>
+          <t>Comparator assumption</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>https://www.transmountain.com/</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>2024</t>
+          <t>Not available</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr"/>
@@ -2584,15 +2597,15 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>lng_canada_ph1_year_1_utilisation</t>
+          <t>coal_tco2e_per_mwh</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.25</v>
+        <v>0.95</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>tCO2e/MWh</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2602,73 +2615,60 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Project-specific ramp for LNG Canada Phase 1, the only Canadian export terminal in operation. Informed by its actual startup: first cargo June 2025, Train 2 producing from November 2025. LNG Canada does not publish utilisation figures, so this is a judgement anchored on observed timing rather than a cited rate.</t>
+          <t>Comparator assumption</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>https://www.lngcanada.ca/</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>Replaces year_1_utilisation for this project only</t>
-        </is>
-      </c>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>lng_canada_ph1_year_2_utilisation</t>
+          <t>tmx_total_system_bpd</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6</v>
+        <v>890000</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>barrels per day</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>assumption</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Second year of the LNG Canada Phase 1 ramp. Judgement, anchored on the observed startup sequence.</t>
+          <t>Trans Mountain system capacity after the May 2024 expansion</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>https://www.lngcanada.ca/</t>
+          <t>https://www.transmountain.com/</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>Replaces year_2_utilisation for this project only</t>
-        </is>
-      </c>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>lng_canada_ph1_steady_state_utilisation</t>
+          <t>lng_canada_ph1_year_1_utilisation</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.85</v>
+        <v>0.25</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Steady state for LNG Canada Phase 1, slightly above the 83.9 per cent global average. Judgement, not a published figure.</t>
+          <t>Project-specific ramp for LNG Canada Phase 1, the only Canadian export terminal in operation. Informed by its actual startup: first cargo June 2025, Train 2 producing from November 2025. LNG Canada does not publish utilisation figures, so this is a judgement anchored on observed timing rather than a cited rate.</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -2697,24 +2697,22 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>Replaces steady_state_utilisation for this project only</t>
+          <t>Replaces year_1_utilisation for this project only</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>liquefaction_drive_default</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>gas_turbine</t>
-        </is>
+          <t>lng_canada_ph1_year_2_utilisation</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.6</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2724,28 +2722,33 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Fallback drive type where a facility does not publish one. Applies only to small domestic and bunkering plants totalling 1.22 mtpa, several predating 2000. The choice between gas turbine and electric moves the total by under 0.2 MtCO2e a year.</t>
+          <t>Second year of the LNG Canada Phase 1 ramp. Judgement, anchored on the observed startup sequence.</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>https://www.lngcanada.ca/</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2025</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Fallback only for domestic plants that still carry not_published. Export and bunkering assets are recorded as gas_turbine. Electric drive is not assumed for any terminal.</t>
+          <t>Replaces year_2_utilisation for this project only</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>saint_john_utilisation</t>
+          <t>lng_canada_ph1_steady_state_utilisation</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.025</v>
+        <v>0.85</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2754,52 +2757,54 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>assumption</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Actual throughput at the Saint John import terminal. Repsol's annual report records 8 TBtu regasified in 2023 and 10 TBtu in 2022, against 7.5 mtpa of nameplate capacity. Corroborated by the CER, which found the terminal at 4 per cent of send-out capacity in 2017, with cargo counts falling from 42 in 2011 to 5 in 2017.</t>
+          <t>Steady state for LNG Canada Phase 1, slightly above the 83.9 per cent global average. Judgement, not a published figure.</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>https://lngprime.com/americas/repsols-saint-john-lng-terminal-to-get-galileos-reliquefaction-tech/115035/</t>
+          <t>https://www.lngcanada.ca/</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Applying nameplate utilisation here overstates the terminal's emissions roughly thirtyfold</t>
+          <t>Replaces steady_state_utilisation for this project only</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>lng_energy_content</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>52</v>
+          <t>liquefaction_drive_default</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>gas_turbine</t>
+        </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MMBtu per tonne</t>
+          <t>category</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>method constant</t>
+          <t>assumption</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Energy content of LNG, used to convert reported throughput in energy units into tonnes.</t>
+          <t>Fallback drive type where a facility does not publish one. Applies only to small domestic and bunkering plants totalling 1.22 mtpa, several predating 2000. The choice between gas turbine and electric moves the total by under 0.2 MtCO2e a year.</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -2809,22 +2814,22 @@
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Also required for the per-kWh energy source comparison</t>
+          <t>Fallback only for domestic plants that still carry not_published. Export and bunkering assets are recorded as gas_turbine. Electric drive is not assumed for any terminal.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>lng_export_licence_max_term</t>
+          <t>saint_john_utilisation</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>50</v>
+        <v>0.025</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2834,193 +2839,188 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Maximum duration of an LNG export licence under the Canadian Energy Regulator Act, raised from 40 years by Bill C-15, Division 41 of Part 5, royal assent 26 March 2026. No 50 year licence has yet been issued: Cedar's licence, approved January 2026, is for 40 years. Precedent suggests holders will apply to extend, as they did when the ceiling rose from 25 to 40 in 2015.</t>
+          <t>Actual throughput at the Saint John import terminal. Repsol's annual report records 8 TBtu regasified in 2023 and 10 TBtu in 2022, against 7.5 mtpa of nameplate capacity. Corroborated by the CER, which found the terminal at 4 per cent of send-out capacity in 2017, with cargo counts falling from 42 in 2011 to 5 in 2017.</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>https://www.parl.ca/documentviewer/en/45-1/bill/C-15/royal-assent</t>
+          <t>https://lngprime.com/americas/repsols-saint-john-lng-terminal-to-get-galileos-reliquefaction-tech/115035/</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>Gives the 50 year lifespan sensitivity a legal basis</t>
+          <t>Applying nameplate utilisation here overstates the terminal's emissions roughly thirtyfold</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>canada_2030_overshoot_gap</t>
+          <t>lng_energy_content</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>200</v>
+        <v>52</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MtCO2e</t>
+          <t>MMBtu per tonne</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>method constant</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Difference between projected 2030 emissions of about 646 MtCO2e and the legislated target range of 417 to 455. Expressing a figure as a share of this gap is harder to dismiss than expressing it as a share of an allowance that is not expected to be met.</t>
+          <t>Energy content of LNG, used to convert reported throughput in energy units into tonnes.</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>https://climateactiontracker.org/countries/canada/</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr"/>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Also required for the per-kWh energy source comparison</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>upstream_ch4_share</t>
+          <t>lng_export_licence_max_term</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3</v>
+        <v>50</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>years</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>assumption</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Share of upstream oil and gas emissions that is methane rather than carbon dioxide. Required to apply the measurement correction and the GWP20 uplift to the methane portion only. Canada's 2023 National Inventory Report gives 20 per cent for the oil and gas sector nationally, but that includes oil sands, which are far more carbon dioxide intensive than gas production. British Columbia is gas-dominated, which raises the share, while its 51 per cent methane reduction by 2023 lowers it.</t>
+          <t>Maximum duration of an LNG export licence under the Canadian Energy Regulator Act, raised from 40 years by Bill C-15, Division 41 of Part 5, royal assent 26 March 2026. No 50 year licence has yet been issued: Cedar's licence, approved January 2026, is for 40 years. Precedent suggests holders will apply to extend, as they did when the ceiling rose from 25 to 40 in 2015.</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>https://gazette.gc.ca/rp-pr/p1/2023/2023-12-16/html/reg3-eng.html</t>
+          <t>https://www.parl.ca/documentviewer/en/45-1/bill/C-15/royal-assent</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Tested across 20 to 40 per cent</t>
+          <t>Gives the 50 year lifespan sensitivity a legal basis</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>upstream_measurement_correction</t>
+          <t>canada_2030_overshoot_gap</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.5</v>
+        <v>200</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>multiplier</t>
+          <t>MtCO2e</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Factor by which peer-reviewed measurement studies find Canadian inventories understate upstream oil and gas methane. Three independent studies agree: 6,650 site measurements across Canada, an Alberta measurement-based inventory, and a British Columbia aircraft survey giving 1.7.</t>
+          <t>Difference between projected 2030 emissions of about 646 MtCO2e and the legislated target range of 417 to 455. Expressing a figure as a share of this gap is harder to dismiss than expressing it as a share of an allowance that is not expected to be met.</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41598-021-87610-3</t>
+          <t>https://climateactiontracker.org/countries/canada/</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>Applied to the methane portion only</t>
-        </is>
-      </c>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>liquefaction_gas_turbine</t>
+          <t>upstream_ch4_share</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>tCO2e per t LNG</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>assumption</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Liquefaction intensity for gas turbine drive, implied by LNG Canada's environmental assessment of roughly 4 MtCO2e per year against 14 mtpa of capacity.</t>
+          <t>Share of upstream oil and gas emissions that is methane rather than carbon dioxide. Required to apply the measurement correction and the GWP20 uplift to the methane portion only. Canada's 2023 National Inventory Report gives 20 per cent for the oil and gas sector nationally, but that includes oil sands, which are far more carbon dioxide intensive than gas production. British Columbia is gas-dominated, which raises the share, while its 51 per cent methane reduction by 2023 lowers it.</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>https://www.projects.eao.gov.bc.ca/p/lng-canada-export-terminal</t>
+          <t>https://gazette.gc.ca/rp-pr/p1/2023/2023-12-16/html/reg3-eng.html</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>Equals Emission Factors liquefaction central. Applied to every terminal for its whole operating life as of August 2026.</t>
+          <t>Tested across 20 to 40 per cent</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>liquefaction_electric</t>
+          <t>upstream_measurement_correction</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.12</v>
+        <v>1.5</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>tCO2e per t LNG</t>
+          <t>multiplier</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3030,28 +3030,33 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Liquefaction intensity for electric drive. Pembina Institute electrified LNG scenario. Woodfibre claims 0.059 for its own facility.</t>
+          <t>Factor by which peer-reviewed measurement studies find Canadian inventories understate upstream oil and gas methane. Three independent studies agree: 6,650 site measurements across Canada, an Alberta measurement-based inventory, and a British Columbia aircraft survey giving 1.7.</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>https://www.pembina.org/</t>
+          <t>https://www.nature.com/articles/s41598-021-87610-3</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2021</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Retained for reference. Not used in the central case. Matches Emission Factors range_low; applies only if electrification is contracted and delivered.</t>
+          <t>Applied to the methane portion only</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>bc_lng_emission_intensity_benchmark</t>
+          <t>liquefaction_gas_turbine</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.16</v>
+        <v>0.29</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -3060,42 +3065,42 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Legislated benchmark under British Columbia's Greenhouse Gas Industrial Reporting and Control Act, covering gas entering the facility to loading onto ships. Facilities above it must buy offsets, buy permits from a better-performing facility, or pay into a technology fund.</t>
+          <t>Liquefaction intensity for gas turbine drive, implied by LNG Canada's environmental assessment of roughly 4 MtCO2e per year against 14 mtpa of capacity.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>https://www2.gov.bc.ca/gov/content/environment/climate-change/industry/reporting</t>
+          <t>https://www.projects.eao.gov.bc.ca/p/lng-canada-export-terminal</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>A gas turbine facility at 0.29 exceeds this by 0.13, about 1.8 Mt/yr across 14 mtpa</t>
+          <t>Equals Emission Factors liquefaction central. Applied to every terminal for its whole operating life as of August 2026.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>route_bc_to_northeast_asia_nm</t>
+          <t>liquefaction_electric</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3800</v>
+        <v>0.12</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>nautical miles</t>
+          <t>tCO2e per t LNG</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3105,37 +3110,32 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Oxford Institute for Energy Studies, west coast Canada to Tokyo, as cited by CAPP. Black &amp; Veatch citing PortWorld gives approximately 4,000 nm for the same run.</t>
+          <t>Liquefaction intensity for electric drive. Pembina Institute electrified LNG scenario. Woodfibre claims 0.059 for its own facility.</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>https://www.capp.ca/wp-content/uploads/2026/05/The-Case-for-Canadian-LNG-April-17-2026.pdf</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>2026</t>
+          <t>https://www.pembina.org/</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>One way</t>
+          <t>Retained for reference. Not used in the central case. Matches Emission Factors range_low; applies only if electrification is contracted and delivered.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>route_us_gulf_to_northeast_asia_nm</t>
+          <t>bc_lng_emission_intensity_benchmark</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>9200</v>
+        <v>0.16</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>nautical miles</t>
+          <t>tCO2e per t LNG</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3145,32 +3145,37 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>US Gulf Coast to Tokyo via the Panama Canal. Reference point only, used to test the industry's proximity claim.</t>
+          <t>Legislated benchmark under British Columbia's Greenhouse Gas Industrial Reporting and Control Act, covering gas entering the facility to loading onto ships. Facilities above it must buy offsets, buy permits from a better-performing facility, or pay into a technology fund.</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>https://www.bv.com/en-US/perspectives/geographic-location-magnifies-advantages-for-north-american-lng-exports</t>
+          <t>https://www2.gov.bc.ca/gov/content/environment/climate-change/industry/reporting</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2016</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>One way</t>
+          <t>A gas turbine facility at 0.29 exceeds this by 0.13, about 1.8 Mt/yr across 14 mtpa</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>voyage_days_bc_to_north_asia</t>
+          <t>route_bc_to_northeast_asia_nm</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>10</v>
+        <v>3800</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>nautical miles</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3180,33 +3185,37 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Reported at the time of LNG Canada's first cargo, against 20 days from the US Gulf Coast via Panama.</t>
+          <t>Oxford Institute for Energy Studies, west coast Canada to Tokyo, as cited by CAPP. Black &amp; Veatch citing PortWorld gives approximately 4,000 nm for the same run.</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>https://www.theglobeandmail.com/business/article-lng-canada-liquefied-natural-gas-shipment-asia/</t>
+          <t>https://www.capp.ca/wp-content/uploads/2026/05/The-Case-for-Canadian-LNG-April-17-2026.pdf</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>One way</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ocean_transport_intensity_range_low</t>
+          <t>route_us_gulf_to_northeast_asia_nm</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.05</v>
+        <v>9200</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>tCO2e per t LNG delivered</t>
+          <t>nautical miles</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3216,33 +3225,32 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Peer reviewed supplier-specific LNG lifecycle assessment. Ocean transport ranges from 0.05 tCO2e/t (short routes) to 0.31 (long routes), a sixfold spread, confirming route matters.</t>
+          <t>US Gulf Coast to Tokyo via the Panama Canal. Reference point only, used to test the industry's proximity claim.</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>https://pubs.acs.org/doi/10.1021/acssuschemeng.1c03307</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr"/>
+          <t>https://www.bv.com/en-US/perspectives/geographic-location-magnifies-advantages-for-north-american-lng-exports</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>One way</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ocean_transport_intensity_range_high</t>
+          <t>voyage_days_bc_to_north_asia</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.31</v>
+        <v>10</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>tCO2e per t LNG delivered</t>
+          <t>days</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3252,17 +3260,17 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Same source. Upper end corresponds to long routes such as US Gulf Coast to Taiwan.</t>
+          <t>Reported at the time of LNG Canada's first cargo, against 20 days from the US Gulf Coast via Panama.</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>https://pubs.acs.org/doi/10.1021/acssuschemeng.1c03307</t>
+          <t>https://www.theglobeandmail.com/business/article-lng-canada-liquefied-natural-gas-shipment-asia/</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -3270,95 +3278,87 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>route_atlantic_routing_factor</t>
+          <t>ocean_transport_intensity_range_low</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.125</v>
+        <v>0.05</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>multiplier</t>
+          <t>tCO2e per t LNG delivered</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Ratio of actual sailing distance to great circle distance for a North Atlantic crossing. Calibrated on Saint John NB to Rotterdam: SeaRates gives 5,648 km (3,050 nm) against a great circle of 2,712 nm. Applied to Atlantic routes only.</t>
+          <t>Peer reviewed supplier-specific LNG lifecycle assessment. Ocean transport ranges from 0.05 tCO2e/t (short routes) to 0.31 (long routes), a sixfold spread, confirming route matters.</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>https://www.searates.com/distance-time/</t>
+          <t>https://pubs.acs.org/doi/10.1021/acssuschemeng.1c03307</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>Not applied to Pacific routes</t>
-        </is>
-      </c>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>route_baie_comeau_to_rotterdam_nm</t>
+          <t>ocean_transport_intensity_range_high</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2980</v>
+        <v>0.31</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>nautical miles</t>
+          <t>tCO2e per t LNG delivered</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Great circle from port coordinates, scaled by the Atlantic routing factor.</t>
+          <t>Same source. Upper end corresponds to long routes such as US Gulf Coast to Taiwan.</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>https://www.searates.com/distance-time/</t>
+          <t>https://pubs.acs.org/doi/10.1021/acssuschemeng.1c03307</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>Estimate, not a published sailing distance</t>
-        </is>
-      </c>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>route_fermeuse_to_rotterdam_nm</t>
+          <t>route_atlantic_routing_factor</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2470</v>
+        <v>1.125</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>nautical miles</t>
+          <t>multiplier</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Great circle from port coordinates, scaled by the Atlantic routing factor.</t>
+          <t>Ratio of actual sailing distance to great circle distance for a North Atlantic crossing. Calibrated on Saint John NB to Rotterdam: SeaRates gives 5,648 km (3,050 nm) against a great circle of 2,712 nm. Applied to Atlantic routes only.</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -3383,18 +3383,18 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>Estimate, not a published sailing distance</t>
+          <t>Not applied to Pacific routes</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>route_saint_john_to_rotterdam_nm</t>
+          <t>route_baie_comeau_to_rotterdam_nm</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3050</v>
+        <v>2980</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -3403,12 +3403,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Actual sailing distance, 5,648 km, from the SeaRates port-to-port calculator.</t>
+          <t>Great circle from port coordinates, scaled by the Atlantic routing factor.</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -3423,62 +3423,62 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>The calibration point for the Atlantic routing factor</t>
+          <t>Estimate, not a published sailing distance</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>lng_carrier_aer_gco2_per_dwt_nm</t>
+          <t>route_fermeuse_to_rotterdam_nm</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>8.5</v>
+        <v>2470</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>gCO2 per DWT per nautical mile</t>
+          <t>nautical miles</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>IMO Data Collection System 2023 annual report, LNG carrier fleet average Annual Efficiency Ratio, as reported in an analysis of EU MRV 2023 data. Annual figure, so it already includes ballast legs.</t>
+          <t>Great circle from port coordinates, scaled by the Atlantic routing factor.</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>https://www.mdpi.com/2077-1312/13/8/1437</t>
+          <t>https://www.searates.com/distance-time/</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>Use to scale shipping by route distance</t>
+          <t>Estimate, not a published sailing distance</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>lng_carrier_kgco2_per_nm</t>
+          <t>route_saint_john_to_rotterdam_nm</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>940</v>
+        <v>3050</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>kg CO2 per nautical mile</t>
+          <t>nautical miles</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3488,112 +3488,117 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>EU JRC analysis of 2019 EU MRV data. LNG carriers are the highest-emitting ship category per nautical mile travelled.</t>
+          <t>Actual sailing distance, 5,648 km, from the SeaRates port-to-port calculator.</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>https://publications.jrc.ec.europa.eu/repository/bitstream/JRC128870/JRC128870_01.pdf</t>
+          <t>https://www.searates.com/distance-time/</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Per ship, not per tonne of cargo</t>
+          <t>The calibration point for the Atlantic routing factor</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>lng_carrier_methane_slip_uplift</t>
+          <t>lng_carrier_aer_gco2_per_dwt_nm</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1.44</v>
+        <v>8.5</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>multiplier</t>
+          <t>gCO2 per DWT per nautical mile</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Derived from the first primary measurement study of an LNG carrier voyage, which recorded 68.1 t CH4 against 4,600 t CO2. At GWP100 of 29.8 this raises voyage emissions by about 44 per cent. Methane slip averaged 3.8 per cent across engines.</t>
+          <t>IMO Data Collection System 2023 annual report, LNG carrier fleet average Annual Efficiency Ratio, as reported in an analysis of EU MRV 2023 data. Annual figure, so it already includes ballast legs.</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>https://pubs.acs.org/doi/10.1021/acs.est.2c01383</t>
+          <t>https://www.mdpi.com/2077-1312/13/8/1437</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>Applies to the shipping stage only</t>
+          <t>Use to scale shipping by route distance</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>cargo_tonnes_per_dwt</t>
+          <t>lng_carrier_kgco2_per_nm</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.85</v>
+        <v>940</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>kg CO2 per nautical mile</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>assumption</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Model assumption - typical ratio of LNG cargo tonnes to carrier deadweight. Needed to convert AER, which is per DWT, into emissions per tonne of cargo.</t>
+          <t>EU JRC analysis of 2019 EU MRV data. LNG carriers are the highest-emitting ship category per nautical mile travelled.</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>https://publications.jrc.ec.europa.eu/repository/bitstream/JRC128870/JRC128870_01.pdf</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2019</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Sensitivity worth testing</t>
+          <t>Per ship, not per tonne of cargo</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>tmx_oil_lifecycle_per_barrel</t>
+          <t>lng_carrier_methane_slip_uplift</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.513</v>
+        <v>1.44</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>tCO2e/bbl</t>
+          <t>multiplier</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3603,53 +3608,128 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Sum of upstream 0.075, transport 0.008 and combustion 0.43</t>
+          <t>Derived from the first primary measurement study of an LNG carrier voyage, which recorded 68.1 t CH4 against 4,600 t CO2. At GWP100 of 29.8 this raises voyage emissions by about 44 per cent. Methane slip averaged 3.8 per cent across engines.</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr"/>
+          <t>https://pubs.acs.org/doi/10.1021/acs.est.2c01383</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>Applies to the shipping stage only</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>cargo_tonnes_per_dwt</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>assumption</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Model assumption - typical ratio of LNG cargo tonnes to carrier deadweight. Needed to convert AER, which is per DWT, into emissions per tonne of cargo.</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>Sensitivity worth testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>tmx_oil_lifecycle_per_barrel</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>tCO2e/bbl</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Sum of upstream 0.075, transport 0.008 and combustion 0.43</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>liquefaction_electrification_assumed</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>assumption</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Model assumption - no external source</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>Not available</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>Electric drive is not assumed for any terminal. Of the projects claiming electrification, only Cedar and Woodfibre have interconnection works under construction; the remainder rest on memoranda of understanding, aspirations conditional on transmission that has not been built, or statements with no firm date. Ksi Lisims holds an MOU with BC Hydro for up to 600 MW conditional on the North Coast Transmission Line expansion, which is not built. LNG Canada Phase 2 states an intention to transition to electric motors as more renewable power becomes available, with no date and no contracted supply. There is not sufficient evidence that electric drive will be in use at these facilities, and a commitment contingent on infrastructure that does not exist is not a basis for lowering the emissions factor. Where electrification is later contracted and built, this assumption should be revisited.</t>
         </is>

--- a/Inputs/Canada_LNG_Data_Inputs.xlsx
+++ b/Inputs/Canada_LNG_Data_Inputs.xlsx
@@ -1413,7 +1413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3732,6 +3732,44 @@
       <c r="H63" t="inlineStr">
         <is>
           <t>Electric drive is not assumed for any terminal. Of the projects claiming electrification, only Cedar and Woodfibre have interconnection works under construction; the remainder rest on memoranda of understanding, aspirations conditional on transmission that has not been built, or statements with no firm date. Ksi Lisims holds an MOU with BC Hydro for up to 600 MW conditional on the North Coast Transmission Line expansion, which is not built. LNG Canada Phase 2 states an intention to transition to electric motors as more renewable power becomes available, with no date and no contracted supply. There is not sufficient evidence that electric drive will be in use at these facilities, and a commitment contingent on infrastructure that does not exist is not a basis for lowering the emissions factor. Where electrification is later contracted and built, this assumption should be revisited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>assumed_first_export_year_if_missing</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>assumption</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Named model parameter: calendar start year filled when Asset Register first_export_year is blank. In-scope assets: tilbury_phase_2, marinvest_baie_comeau, summit_lake_pg_lng, fermeuse_energy_flng, discovery_t1t4, kanata_lng. With licence-end stops, every dated authorised end year is 2056-2066; the published panel tail is entirely this placeholder.</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Central value 2030. Sensitivity at 2033 and 2035 is reported. Summit Lake states a 30-year life; the other five use lifecycle_years_default.</t>
         </is>
       </c>
     </row>

--- a/Inputs/Canada_LNG_Data_Inputs.xlsx
+++ b/Inputs/Canada_LNG_Data_Inputs.xlsx
@@ -1413,7 +1413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3770,6 +3770,82 @@
       <c r="H64" t="inlineStr">
         <is>
           <t>Central value 2030. Sensitivity at 2033 and 2035 is reported. Summit Lake states a 30-year life; the other five use lifecycle_years_default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>monte_carlo_seed</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>20260828</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>assumption</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Seed for the decoupled physics Monte Carlo (numpy Generator). Recorded in the run manifest.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Do not reuse a draw sequence across published runs without recording a new seed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>monte_carlo_n_draws</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>assumption</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Number of physics draws. Price schedules are applied after, not rebuilt inside the loop.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>10,000 draws for stable 5th/95th percentiles.</t>
         </is>
       </c>
     </row>

--- a/Inputs/Canada_LNG_Data_Inputs.xlsx
+++ b/Inputs/Canada_LNG_Data_Inputs.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Across all Canadian LNG assets, about 16 per cent of emissions are Canada territorial, 5 per cent are international bunkers, and 80 per cent are foreign territorial. LNG carrier shipping is itself an international bunker, so it lands nowhere.</t>
+          <t>Across all Canadian LNG assets, 18.5 per cent of emissions are Canada territorial, 5.6 per cent are international bunkers, and 75.9 per cent are foreign territorial. LNG carrier shipping is itself an international bunker, so it lands nowhere. These shares are the life-average split; the model asserts them every run.</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="P2" s="4" t="inlineStr">
         <is>
-          <t>Only about 16 per cent of these emissions land on Canada's inventory. The rest is counted by the importing country or by nobody.</t>
+          <t>18 per cent of export-chain emissions land on Canada's inventory, 3 per cent are international bunkers, and 79 per cent are foreign territorial (importing-country inventory).</t>
         </is>
       </c>
     </row>
@@ -4549,7 +4549,7 @@
       </c>
       <c r="P3" s="4" t="inlineStr">
         <is>
-          <t>Under UNFCCC accounting international bunkers are reported separately and attributed to no country. Roughly 80 per cent of this chain's emissions land nowhere.</t>
+          <t>Under UNFCCC accounting international bunkers are reported separately and attributed to no country. 81 per cent of this chain's emissions are bunkers (land nowhere); the remaining 19 per cent is Canada territorial (upstream, pipeline, liquefaction).</t>
         </is>
       </c>
     </row>

--- a/Inputs/Canada_LNG_Data_Inputs.xlsx
+++ b/Inputs/Canada_LNG_Data_Inputs.xlsx
@@ -1413,7 +1413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H66"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3846,6 +3846,86 @@
       <c r="H66" t="inlineStr">
         <is>
           <t>10,000 draws for stable 5th/95th percentiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>headline_scope_chains</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>export</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>comma-separated chains</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>assumption</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Model assumption - no external source</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Headline results include assets whose chain is in headline_scope_chains and whose calc_group is in headline_scope_calc_groups. Domestic peak-shaving and other non-export assets are out of headline; they stay in the register. Inventing a 1971/1976 retirement date is not supported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>headline_scope_calc_groups</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>operating,under_construction,proposed</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>comma-separated calc_groups</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>assumption</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Model assumption - no external source</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Headline results include assets whose chain is in headline_scope_chains and whose calc_group is in headline_scope_calc_groups. Domestic peak-shaving and other non-export assets are out of headline; they stay in the register. Inventing a 1971/1976 retirement date is not supported.</t>
         </is>
       </c>
     </row>

--- a/Inputs/Canada_LNG_Data_Inputs.xlsx
+++ b/Inputs/Canada_LNG_Data_Inputs.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Across all Canadian LNG assets, 18.5 per cent of emissions are Canada territorial, 5.6 per cent are international bunkers, and 75.9 per cent are foreign territorial. LNG carrier shipping is itself an international bunker, so it lands nowhere. These shares are the life-average split; the model asserts them every run.</t>
+          <t>Across the export-chain headline (headline_scope_chains=export; headline_scope_calc_groups=operating,under_construction,proposed), 18.0 per cent of emissions are Canada territorial, 3.4 per cent are international bunkers, and 78.6 per cent are foreign territorial. LNG carrier shipping is itself an international bunker, so it lands nowhere. These shares are the life-average split; the model asserts them every run. Eight non-export assets totalling 242.9 MtCO2e stay in the register.</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
-          <t>45.4 mtpa active, 12.7 mtpa early stage</t>
+          <t>100.1 mtpa (14.0 operating, 5.4 under construction, 80.7 proposed)</t>
         </is>
       </c>
       <c r="P2" s="4" t="inlineStr">

--- a/Inputs/Canada_LNG_Data_Inputs.xlsx
+++ b/Inputs/Canada_LNG_Data_Inputs.xlsx
@@ -4784,7 +4784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4984,6 +4984,102 @@
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Literature band adjusted by feedgas pipeline allocation share where a pipeline is matched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>upstream_ch4_derived_co2e</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>(derived at build)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CH4-derived part of the upstream factor, per tonne LNG. The official inventory factor times (1 - upstream_ch4_share) is the CO2 part; any excess of the scenario upstream factor over that is methane-derived CO2e. This is the construction the upstream factor is built from, not a new assumption.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>tCO2e per t LNG</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>max(upstream factor for the scenario - inventory_as_reported x (1 - upstream_ch4_share), 0). At measurement_central: 0.25 - 0.22 x 0.7 = 0.096.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>shipping_ch4_derived_co2e_share</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>(derived at build)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CH4-derived share of the shipping stage's CO2e. The 1.44 LNG carrier uplift in the shipping factor's own derivation is entirely measured methane slip, so that share of the shipping CO2e is methane rather than CO2.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1 - 1 / lng_carrier_methane_slip_uplift = 1 - 1/1.44 = 0.3056. At the 0.12 central shipping factor that is 0.0367 tCO2e per t LNG.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ch4_mass_kt</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>(derived at build)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Methane mass behind the CH4-derived CO2e in an asset-year. Not defined for the near_term_methane_gwp20 scenario, whose upstream factor (0.22 x 1.5) is not a GWP100 CO2e figure; that scenario's cell is left blank rather than divided by the wrong GWP.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>kt CH4</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ch4_derived_co2e_mt / gwp100_ch4 x 1000. Pipeline fugitive methane is not split and is not in this mass; liquefaction, regasification and combustion are treated as CO2.</t>
         </is>
       </c>
     </row>

--- a/Inputs/Canada_LNG_Data_Inputs.xlsx
+++ b/Inputs/Canada_LNG_Data_Inputs.xlsx
@@ -693,7 +693,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Across the export-chain headline (headline_scope_chains=export; headline_scope_calc_groups=operating,under_construction,proposed), 18.0 per cent of emissions are Canada territorial, 3.4 per cent are international bunkers, and 78.6 per cent are foreign territorial. LNG carrier shipping is itself an international bunker, so it lands nowhere. These shares are the life-average split; the model asserts them every run. Eight non-export assets totalling 242.9 MtCO2e stay in the register.</t>
+          <t>Across the export-chain headline (headline_scope_chains=export; headline_scope_calc_groups=operating,under_construction,proposed), 18.1 per cent of emissions are Canada territorial, 3.2 per cent are international bunkers, and 78.7 per cent are foreign territorial. LNG carrier shipping is itself an international bunker, so it lands nowhere. These shares are the life-average split; the model asserts them every run. Shipping is scaled per asset by route_distance_nm / route_bc_to_northeast_asia_nm, which is what moved the bunkers share down from 3.4 per cent. Eight non-export assets totalling 242.9 MtCO2e stay in the register.</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Baie-Comeau to Rotterdam is about 2,980 nautical miles and Fermeuse about 2,470, against 3,800 from British Columbia to Asia. East coast projects therefore carry lower shipping emissions than west coast ones. The routing factor is not applied to Pacific routes, where the cited figure is used.</t>
+          <t>Baie-Comeau to Rotterdam is about 2,980 nautical miles and Fermeuse about 2,470, against 3,800 from British Columbia to Asia. East coast projects therefore carry lower shipping emissions than west coast ones, and the model implements this: shipping intensity for each asset is the 0.12 central factor times route_distance_nm / route_bc_to_northeast_asia_nm. An asset on a chain that includes the shipping stage with a blank route_distance_nm raises rather than defaulting to the BC basis. Bunkering has no shipping stage. The routing factor is not applied to Pacific routes, where the cited figure is used. The lifecycle comparison in src/lca_comparison.py deliberately stays on the unscaled BC basis, because the comparator studies are single-route.</t>
         </is>
       </c>
     </row>

--- a/Inputs/Canada_LNG_Data_Inputs.xlsx
+++ b/Inputs/Canada_LNG_Data_Inputs.xlsx
@@ -1413,7 +1413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3926,6 +3926,86 @@
       <c r="H68" t="inlineStr">
         <is>
           <t>Headline results include assets whose chain is in headline_scope_chains and whose calc_group is in headline_scope_calc_groups. Domestic peak-shaving and other non-export assets are out of headline; they stay in the register. Inventing a 1971/1976 retirement date is not supported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>liquefaction_electric_drive_gas_generation</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>tCO2e per t LNG</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>British Columbia Environmental Assessment Office, Assessment Report for Ksi Lisims LNG, 7 August 2025, Canadian Impact Assessment Registry document 163192E, pages 847 to 848 - Alternative Case, gas-fired power barges</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>https://iaac-aeic.gc.ca/050/documents/p82797/163192E.pdf</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>SENSITIVITY ONLY - the central liquefaction factor stays 0.29 for every terminal. BOUNDARY: this is the facility total intensity including marine sources, not the liquefaction stage alone, so it is not like for like with the 0.29 liquefaction factor on the Emission Factors sheet. Any comparison against 0.29 is therefore approximate and is labelled as such wherever it is reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>liquefaction_electric_drive_grid</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>tCO2e per t LNG</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>British Columbia Environmental Assessment Office, Assessment Report for Ksi Lisims LNG, 7 August 2025, Canadian Impact Assessment Registry document 163192E, pages 847 to 848 - Base Case, grid supply</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>https://iaac-aeic.gc.ca/050/documents/p82797/163192E.pdf</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>SENSITIVITY ONLY - the central liquefaction factor stays 0.29 for every terminal. BOUNDARY: this is the facility total intensity including marine sources, not the liquefaction stage alone, so it is not like for like with the 0.29 liquefaction factor on the Emission Factors sheet. Any comparison against 0.29 is therefore approximate and is labelled as such wherever it is reported.</t>
         </is>
       </c>
     </row>

--- a/Inputs/Canada_LNG_Data_Inputs.xlsx
+++ b/Inputs/Canada_LNG_Data_Inputs.xlsx
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Literature band, independently validated. The BC Environmental Assessment Office assessed Coastal GasLink at 3.517 MtCO2e/yr at its full 5 Bcf/d design capacity. Scaled to the 2.1 Bcf/d serving LNG Canada Phase 1 that implies 1.48 MtCO2e/yr against our model's 1.47, a difference of 0.6 per cent.</t>
+          <t>Assumed 0.10 tCO2e per t LNG. No ICF or Sphera document stating this figure was located. The BC Environmental Assessment Office Coastal GasLink assessment (October 2014) reports 3.517 MtCO2e/yr at 5 Bcf/d design capacity. Scaled to the 2.1 Bcf/d serving LNG Canada Phase 1 that implies 1.48 MtCO2e/yr against this model's 1.47 at 0.10 t/t. That check confirms the arithmetic of scaling the assumed factor, not an independent measurement of 0.10.</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>ICF and Sphera studies cited in BC EAO LNG reviews. Validation source: BC Environmental Assessment Office 2014 Coastal GasLink assessment report.</t>
+          <t>Range 0.05-0.18 is an assumed literature band, not a cited interval. Consistency check: BC EAO 2014 Coastal GasLink Assessment Report, https://projects.eao.gov.bc.ca/api/document/58868fd3e036fb0105768772/fetch/Assessment%20Report%20and%20Appendices%20for%20the%20CGL%20Project%20dated%20October%202014..pdf</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>range_low 0.12 is the electric-drive factor (Pembina Institute electrified LNG scenario). It applies only if electrification is contracted and delivered. It is not used in the central case. range_high 0.36 remains the literature upper bound for gas-turbine plants. British Columbia legislates a benchmark of 0.16 tCO2e per tonne LNG covering gas entering the facility to loading onto ships, under the Greenhouse Gas Industrial Reporting and Control Act.</t>
+          <t>range_low 0.12 is a declared assumption previously attributed to a Pembina Institute electrified-LNG scenario. No Pembina document stating 0.12 tCO2e/t was located (Squaring the Circle 2023 uses 0.15 / 0.059 / 0.04 for specific BC terminals; Wellhead to Waterline 2014 reports a 0.11 t/t reduction from electrification, not a 0.12 absolute intensity). It is not used in the central case. range_high 0.36 remains an assumed literature upper bound. BC GGIRCA benchmark 0.16 is recorded on the Parameters sheet and is not this row's central.</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -1341,12 +1341,12 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>RMI Oil Climate Index benchmarks. Occurs overseas, so no Canadian source applies.</t>
+          <t>Assumed 0.04 tCO2e per t LNG. Previously labelled RMI Oil Climate Index; no OCI+ table or page states 0.04 t/t. A peer-reviewed US LNG LCA (Gan et al. 2024, Communications Earth &amp; Environment) places regasification at 0.021 tCO2e/t, which sits at this row's range_low. The central 0.04 is a judgement in the middle of the 0.02-0.06 assumed range.</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>RMI Oil Climate Index. Corroborated by a peer-reviewed lifecycle assessment placing regasification at 0.021 tCO2e per tonne delivered.</t>
+          <t>Range is an assumed band. Corroboration at the low end: Gan et al. 2024 https://doi.org/10.1038/s43247-024-01988-2 (0.021 tCO2e/t). RMI OCI+ (https://ociplus.rmi.org/total-emissions) does not publish a 0.04 t/t LNG regasification factor.</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -1413,7 +1413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>IGU World LNG Report 2026 - global average liquefaction utilisation 83.9% in 2025</t>
+          <t>IGU World LNG Report 2026: global average liquefaction utilisation 83.9% in 2025 (decline from 86.5% in 2024).</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>https://www.igu.org/</t>
+          <t>https://www.igu.org/advocacy/graphics-data/2026-world-lng-report-03</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1502,7 +1502,11 @@
           <t>2025 data</t>
         </is>
       </c>
-      <c r="H2" s="4" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Figure also in the report PDF https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf (liquefaction capacity chapter). Nameplate utilisation, not available-capacity.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1633,7 +1637,7 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Run as a sensitivity, not fixed</t>
+          <t>Fallback only. Licensed assets use authorised_export_end_year, sourced to the licence filing on Asset Sources (GL-330, GL-340, GL-346, GL-349), not this index page.</t>
         </is>
       </c>
     </row>
@@ -2646,20 +2650,24 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Trans Mountain system capacity after the May 2024 expansion</t>
+          <t>Trans Mountain Corporation, Management's Discussion and Analysis, 31 March 2025: mechanical completion and commercial commencement of TMEP in Q2 2024 expanded the system to a combined nominal capacity of 890,000 bpd.</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>https://www.transmountain.com/</t>
+          <t>https://docs.transmountain.com/Corporate-Reports/TMC-03.31.25-Management-Report-Final.pdf</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="inlineStr"/>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Nominal / nameplate capacity. Actual throughput runs below this.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2949,12 +2957,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>assumption</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Difference between projected 2030 emissions of about 646 MtCO2e and the legislated target range of 417 to 455. Expressing a figure as a share of this gap is harder to dismiss than expressing it as a share of an allowance that is not expected to be met.</t>
+          <t>Round figure in the neighbourhood of projected 2030 emissions (646 Mt) minus the 417-455 Mt target range (arithmetic interval 191-229). 200 is a judgement, not the difference of two cells.</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2967,7 +2975,11 @@
           <t>2026</t>
         </is>
       </c>
-      <c r="H43" s="4" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Typed assumption. The interval is 191 to 229 Mt.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3105,22 +3117,22 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>assumption</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Liquefaction intensity for electric drive. Pembina Institute electrified LNG scenario. Woodfibre claims 0.059 for its own facility.</t>
+          <t>Declared assumption. Previously cited as Pembina Institute electrified LNG; no Pembina document stating 0.12 tCO2e/t was located. Retained as the figure-8 counterfactual and Emission Factors range_low. Not used in the central case. EAO 0.021 / 0.156 are a separate SI.</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>https://www.pembina.org/</t>
+          <t>Not available</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Retained for reference. Not used in the central case. Matches Emission Factors range_low; applies only if electrification is contracted and delivered.</t>
+          <t>Pembina Squaring the Circle (2023) uses 0.15 (LNG Canada Phase 1), 0.059 (Phase 2) and 0.04 (Woodfibre), not 0.12. https://www.pembina.org/reports/squaring-the-circle-state-of-lng-2023.pdf</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3695,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Sum of upstream 0.075, transport 0.008 and combustion 0.43</t>
+          <t>Sum of tmx_oil_upstream_per_barrel (0.075) + tmx_oil_transport_per_barrel (0.008) + tmx_oil_combustion_per_barrel (0.43). See those rows for sources.</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -3691,7 +3703,11 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr"/>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>Derived identity. Oil runs at nameplate x 365 x 40 years, unlike LNG. Figure 7 states the utilisation asymmetry. Alberta bitumen is not given its own heavier upstream factor.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4006,6 +4022,558 @@
       <c r="H70" t="inlineStr">
         <is>
           <t>SENSITIVITY ONLY - the central liquefaction factor stays 0.29 for every terminal. BOUNDARY: this is the facility total intensity including marine sources, not the liquefaction stage alone, so it is not like for like with the 0.29 liquefaction factor on the Emission Factors sheet. Any comparison against 0.29 is therefore approximate and is labelled as such wherever it is reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>tmx_oil_upstream_per_barrel</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>tCO2e/bbl</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Natural Resources Canada, Roadmap for the Decarbonization of Canada's Oil and Gas Sector: 2021 oil sands production intensity approximately 75 kg CO2e/barrel. Slate: Canadian oil sands average, not a TMX ticket-by-ticket mix. TMX also carries conventional crude (NRCan ~48-49 kg/bbl), so 0.075 is oil-sands-heavy for the TMX mix.</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>https://natural-resources.canada.ca/climate-change/roadmap-decarbonization-canada-s-oil-gas-sector</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Upstream production only. Not well-to-tank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>tmx_oil_transport_per_barrel</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>tCO2e/bbl</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>assumption</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Declared assumption. 8 kgCO2e/bbl for pipeline transport. No document stating this figure for TMX was located.</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Not a cited TMX intensity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>tmx_oil_combustion_per_barrel</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>tCO2e/bbl</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>IPCC 2006 Guidelines, Volume 2, Chapter 1: crude oil default NCV 42.3 TJ/Gg (Table 1.2) and carbon content 20.0 kg C/GJ (Table 1.3) give 0.423 tCO2/bbl at 100% oxidation; stored as 0.43. Slate: IPCC generic crude, not a WCSB or TMX assay.</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>https://www.ipcc-nggip.iges.or.jp/public/2006gl/pdf/2_Volume2/V2_1_Ch1_Introduction.pdf</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Combustion CO2 only. Rounding 0.423 to 0.43 is undeclared at the third decimal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>tmx_expansion_bpd</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>590000</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>barrels per day</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Increment implied by the expanded-system 890,000 bpd less the pre-expansion ~300,000 bpd, both stated in Trans Mountain's description of the May 2024 expansion.</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>https://www.transmountain.com/news/trans-mountain-pipeline-system-a-strategic-canadian-asset</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>890,000 - 300,000 = 590,000. Figure 7 expansion-only bar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>days_per_year</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>365</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>method constant</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Civil year used to convert barrels per day to an annual total for the oil comparator. Not a leap-year correction.</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Structural method constant. LNG utilisation is a fraction of nameplate, not a day count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>lca_howarth_gwp20_low</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>tCO2e per t LNG</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Howarth 2024, Energy Science &amp; Engineering, Table 3, GWP20, average 38-day voyage.</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/ese3.1934</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Figure 10 only. Not mixed with this model's GWP100 totals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>lca_howarth_gwp20_high</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>tCO2e per t LNG</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Howarth 2024 Table 3, GWP20 upper end of the four tanker types.</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/ese3.1934</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Figure 10 only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>lca_roman_white_w2r_p025</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>tCO2e per t LNG</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Roman-White et al. 2021, ACS Sustainable Chemistry &amp; Engineering, Table 1, China, GWP100, cradle to regasification, P2.5.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1021/acssuschemeng.1c03307</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Figure 10 only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>lca_roman_white_w2r_expected</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>tCO2e per t LNG</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Roman-White et al. 2021 Table 1 expected value, not an arithmetic midpoint.</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1021/acssuschemeng.1c03307</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Figure 10 only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>lca_roman_white_w2r_p975</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>tCO2e per t LNG</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Roman-White et al. 2021 Table 1, P97.5.</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1021/acssuschemeng.1c03307</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Figure 10 only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>lca_balcombe_lng_stages_low_g_per_mj_hhv</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>gCO2e per MJ HHV</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Balcombe et al. 2016 literature range, liquefaction + tanker + regasification.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/ese3.161</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Figure 10. Converted with lca_hhv_mj_per_kg.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>lca_balcombe_lng_stages_high_g_per_mj_hhv</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>gCO2e per MJ HHV</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Balcombe et al. 2016 literature range, upper end.</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/ese3.161</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Figure 10.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>lca_hhv_mj_per_kg</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>55</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>MJ per kg</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>cited</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Higher heating value used by Balcombe et al. to report LNG-stage intensities. Not this model's lng_energy_content (52).</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1002/ese3.161</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Figure 10 conversion only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>placeholder_sensitivity_years</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2033,2035</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>assumption</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Sensitivity start years for assets with a blank first_export_year. Central remains assumed_first_export_year_if_missing (2030). These years are not filed dates.</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>SI only. Do not treat as filed first-export years.</t>
         </is>
       </c>
     </row>
@@ -4376,12 +4944,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>upstream 0.33</t>
+          <t>upstream 0.428</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>x1.5, then GWP20 on the methane portion</t>
+          <t>x1.5 on the methane portion of the inventory, then GWP20/GWP100 (82.5/29.8) on that methane portion only</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4391,12 +4959,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Methane's 20 year warming potential, applied to the methane portion only</t>
+          <t>Non-methane portion of inventory_as_reported (0.22 x 0.70 = 0.154) is unchanged. Methane portion is inventory x upstream_ch4_share x upstream_measurement_correction x (gwp20_ch4 / gwp100_ch4). Depends on the assumed methane share of 0.30. Was 0.33 (= 0.22 x 1.5 on the whole factor); that treated all upstream as methane.</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Not to the whole factor</t>
+          <t>Result 0.428 depends on upstream_ch4_share = 0.30. Pipeline methane is not re-weighted: no pipeline methane share exists.</t>
         </is>
       </c>
     </row>
@@ -4632,7 +5200,7 @@
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
-          <t>100.1 mtpa (14.0 operating, 5.4 under construction, 80.7 proposed)</t>
+          <t>80.1 mtpa (14.0 operating, 5.4 under construction, 60.7 proposed)</t>
         </is>
       </c>
       <c r="P2" s="4" t="inlineStr">
@@ -5175,7 +5743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5346,6 +5914,134 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>pipeline_transport central 0.10</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Emission Factors:pipeline_transport</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>assumption, declared</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>No ICF or Sphera document stating 0.10 tCO2e/t was located. The CGL 1.47 vs 1.48 check confirms scaling of the assumed factor, not an independent measurement.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>A cited pipeline LCA or inventory intensity for BC gas transmission.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>medium - about 3% of the lifecycle total</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>regasification central 0.04</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Emission Factors:regasification</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>assumption, declared</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Previously labelled RMI Oil Climate Index; OCI+ does not publish 0.04 t/t.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>A named OCI+ or peer-reviewed regasification intensity used as central.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>low - about 1% of the lifecycle total</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>liquefaction_electric 0.12</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Parameters:liquefaction_electric; Emission Factors range_low</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>assumption, declared</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>No Pembina document stating 0.12 tCO2e/t was located.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>A Pembina table, or replacement by the EAO 0.021/0.156 pair as the electric counterfactual.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>low - not used in the central case</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tmx_oil_transport_per_barrel</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Parameters:tmx_oil_transport_per_barrel</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>assumption, declared, 0.008 tCO2e/bbl</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>No TMX or CER document stating 8 kgCO2e/bbl was located.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>A TMX or OPGEE/GHGenius transport intensity for the Edmonton-Burnaby haul.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>low - figure 7 only</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Inputs/Canada_LNG_Data_Inputs.xlsx
+++ b/Inputs/Canada_LNG_Data_Inputs.xlsx
@@ -1242,7 +1242,7 @@
         <v>0.29</v>
       </c>
       <c r="F4" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="G4" t="n">
         <v>0.36</v>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>range_low 0.12 is a declared assumption previously attributed to a Pembina Institute electrified-LNG scenario. No Pembina document stating 0.12 tCO2e/t was located (Squaring the Circle 2023 uses 0.15 / 0.059 / 0.04 for specific BC terminals; Wellhead to Waterline 2014 reports a 0.11 t/t reduction from electrification, not a 0.12 absolute intensity). It is not used in the central case. range_high 0.36 remains an assumed literature upper bound. BC GGIRCA benchmark 0.16 is recorded on the Parameters sheet and is not this row's central.</t>
+          <t>range_low 0.15 tCO2e per t LNG: Pembina Institute, Squaring the Circle: State of LNG 2023, https://www.pembina.org/reports/squaring-the-circle-state-of-lng-2023.pdf , reported figure for LNG Canada Phase 1 under electric drive. Adopted 3 September 2026, replacing 0.12, which no Pembina document states and which appears to have been a misreading of the 0.11 tCO2e/t REDUCTION reported in Wellhead to Waterline (2014) as an absolute intensity. The same Pembina report gives 0.059 for LNG Canada Phase 2 and 0.04 for Woodfibre; those are facility-specific and are not used. range_low is a counterfactual for the figure-8 appendix only and is not used in the central case. range_high 0.36 remains an uncited literature upper bound for gas-turbine plants. Corroboration on the central: IEA (2025), page 13, gives a global average liquefaction intensity of about 6 g CO2-eq/MJ of LNG, which at 55 MJ/kg is 0.33 tCO2e/t - above this model's 0.29, so 0.29 is not a high-side choice. https://iea.blob.core.windows.net/assets/df9b1bed-4e16-4db8-bec5-a5fa117a9130/AssessingemissionsfromLNGsupplyandabatementoptions.pdf</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -1331,27 +1331,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.04</v>
+        <v>0.021</v>
       </c>
       <c r="F6" t="n">
-        <v>0.02</v>
+        <v>0.011</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06</v>
+        <v>0.0275</v>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>Assumed 0.04 tCO2e per t LNG. Previously labelled RMI Oil Climate Index; no OCI+ table or page states 0.04 t/t. A peer-reviewed US LNG LCA (Gan et al. 2024, Communications Earth &amp; Environment) places regasification at 0.021 tCO2e/t, which sits at this row's range_low. The central 0.04 is a judgement in the middle of the 0.02-0.06 assumed range.</t>
+          <t>0.021 tCO2e per t LNG. Gan et al. (2024), Communications Earth &amp; Environment, https://doi.org/10.1038/s43247-024-01988-2 : peer-reviewed US LNG lifecycle assessment placing regasification at 0.021 tCO2e/t. Adopted 3 September 2026, replacing an uncited 0.04 that sat above the top of the IEA range below. The previous 0.04 was labelled RMI Oil Climate Index; no OCI+ table or page states 0.04 t/t.</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Range is an assumed band. Corroboration at the low end: Gan et al. 2024 https://doi.org/10.1038/s43247-024-01988-2 (0.021 tCO2e/t). RMI OCI+ (https://ociplus.rmi.org/total-emissions) does not publish a 0.04 t/t LNG regasification factor.</t>
+          <t>IEA (2025), Assessing Emissions from LNG Supply and Abatement Options, IEA, Paris, CC BY 4.0, page 16: "Total GHG emissions from regasification are around 0.2-0.5 g CO2-eq/MJ of gas regasified." https://iea.blob.core.windows.net/assets/df9b1bed-4e16-4db8-bec5-a5fa117a9130/AssessingemissionsfromLNGsupplyandabatementoptions.pdf . Converted at the report's own stated basis of 55 MJ per kg of methane (footnote 2, page 7): 0.2 g/MJ = 0.011 and 0.5 g/MJ = 0.0275 tCO2e per tonne. IEA takes 1 t methane as 30 t CO2 on a 100-year GWP, against this model's 29.8. The Gan et al. central of 0.021 sits inside this range.</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Smallest stage, about 1 per cent of the total. Varies with the destination terminal's design and whether waste heat is recovered.</t>
+          <t>Smallest stage, about 0.6 per cent of the lifecycle total after the move to 0.021. Varies with the destination terminal's technology: open-rack vaporisers (about 90 per cent of world plants) draw power for pumps and boil-off compressors, while submerged combustion vaporisers burn gas directly. IEA reports regasification energy demand at 0.3-0.5 per cent of the LNG imported.</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
         <v>2.75</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="G7" t="n">
         <v>3</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Range reflects variation in delivered gas composition, principally heavier hydrocarbon content.</t>
+          <t>Derived from the IPCC 2006 Guidelines Volume 2 Chapter 1 uncertainty ranges, https://www.ipcc-nggip.iges.or.jp/public/2006gl/pdf/2_Volume2/V2_1_Ch1_Introduction.pdf . Table 1.2 natural gas NCV 48.0 TJ/Gg (lower 46.5, upper 50.4) and Table 1.3 carbon content 15.3 kgC/GJ (lower 14.8, upper 15.9), both 95% confidence intervals. NCV x carbon content x 44/12 gives 2.523 / 2.693 / 2.938 tCO2 per tonne. Cross-check: Table 2.2 gives 56,100 kgCO2/TJ, which x 48.0 TJ/Gg = 2.693, consistent. The IPCC central is pipeline natural gas at 2.693; this model's central is 2.75, the stoichiometric value for pure methane (44/16), which is the right central for LNG because liquefaction strips inerts and heavier fractions. The IPCC RELATIVE uncertainty (0.937 / 1.091) applied to 2.75 gives 2.58 / 3.00. The two uncertainty ranges are combined multiplicatively, which is conservative (it treats NCV and carbon content as perfectly correlated). Previous range_low was 2.50, wider than the IPCC interval supports and uncited.</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1413,7 +1413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H84"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Method constant used for feedgas allocation share</t>
+          <t>Volume of natural gas from one Mt of LNG, used for feedgas headroom against pipeline capacity and the Fermeuse capacity derivation. Basis: LNG density about 450 kg/m3 and a liquid-to-gas expansion ratio near 600:1 at 15 degrees C and 101.325 kPa. The Energy Institute Statistical Review conversion gives 1.36 bcm per Mt on its own density and reference conditions; 1.38 is 1.5% higher and is retained. At 1.36 the Fermeuse derivation gives 5.05 mtpa rather than 4.98, so it rounds to 5.0 either way and no published figure moves.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>No external citation identified</t>
+          <t>Read by no module; it backs the stored feedgas_demand_bcm_y and headroom_bcm_y columns on the register's Supporting Infrastructure sheet. Basis recorded 3 September 2026; previously an uncited method constant.</t>
         </is>
       </c>
     </row>
@@ -2632,30 +2632,30 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>tmx_total_system_bpd</t>
+          <t>lng_canada_ph1_year_1_utilisation</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>890000</v>
+        <v>0.25</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>barrels per day</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>assumption</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Trans Mountain Corporation, Management's Discussion and Analysis, 31 March 2025: mechanical completion and commercial commencement of TMEP in Q2 2024 expanded the system to a combined nominal capacity of 890,000 bpd.</t>
+          <t>Project-specific ramp for LNG Canada Phase 1, the only Canadian export terminal in operation. Informed by its actual startup: first cargo June 2025, Train 2 producing from November 2025. LNG Canada does not publish utilisation figures, so this is a judgement anchored on observed timing rather than a cited rate.</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>https://docs.transmountain.com/Corporate-Reports/TMC-03.31.25-Management-Report-Final.pdf</t>
+          <t>https://www.lngcanada.ca/</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2665,18 +2665,18 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Nominal / nameplate capacity. Actual throughput runs below this.</t>
+          <t>Replaces year_1_utilisation for this project only</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>lng_canada_ph1_year_1_utilisation</t>
+          <t>lng_canada_ph1_year_2_utilisation</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Project-specific ramp for LNG Canada Phase 1, the only Canadian export terminal in operation. Informed by its actual startup: first cargo June 2025, Train 2 producing from November 2025. LNG Canada does not publish utilisation figures, so this is a judgement anchored on observed timing rather than a cited rate.</t>
+          <t>Second year of the LNG Canada Phase 1 ramp. Judgement, anchored on the observed startup sequence.</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -2705,18 +2705,18 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>Replaces year_1_utilisation for this project only</t>
+          <t>Replaces year_2_utilisation for this project only</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>lng_canada_ph1_year_2_utilisation</t>
+          <t>lng_canada_ph1_steady_state_utilisation</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6</v>
+        <v>0.85</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Second year of the LNG Canada Phase 1 ramp. Judgement, anchored on the observed startup sequence.</t>
+          <t>Steady state for LNG Canada Phase 1, slightly above the 83.9 per cent global average. Judgement, not a published figure.</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -2745,22 +2745,24 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Replaces year_2_utilisation for this project only</t>
+          <t>Replaces steady_state_utilisation for this project only</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>lng_canada_ph1_steady_state_utilisation</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>0.85</v>
+          <t>liquefaction_drive_default</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>gas_turbine</t>
+        </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>category</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2770,74 +2772,72 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Steady state for LNG Canada Phase 1, slightly above the 83.9 per cent global average. Judgement, not a published figure.</t>
+          <t>Fallback drive type where a facility does not publish one. Applies only to small domestic and bunkering plants totalling 1.22 mtpa, several predating 2000. The choice between gas turbine and electric moves the total by under 0.2 MtCO2e a year.</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>https://www.lngcanada.ca/</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2025</t>
+          <t>Not available</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>Replaces steady_state_utilisation for this project only</t>
+          <t>Fallback only for domestic plants that still carry not_published. Export and bunkering assets are recorded as gas_turbine. Electric drive is not assumed for any terminal.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>liquefaction_drive_default</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>gas_turbine</t>
-        </is>
+          <t>saint_john_utilisation</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.025</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>assumption</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Fallback drive type where a facility does not publish one. Applies only to small domestic and bunkering plants totalling 1.22 mtpa, several predating 2000. The choice between gas turbine and electric moves the total by under 0.2 MtCO2e a year.</t>
+          <t>Actual throughput at the Saint John import terminal. Repsol's annual report records 8 TBtu regasified in 2023 and 10 TBtu in 2022, against 7.5 mtpa of nameplate capacity. Corroborated by the CER, which found the terminal at 4 per cent of send-out capacity in 2017, with cargo counts falling from 42 in 2011 to 5 in 2017.</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>https://lngprime.com/americas/repsols-saint-john-lng-terminal-to-get-galileos-reliquefaction-tech/115035/</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2023</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>Fallback only for domestic plants that still carry not_published. Export and bunkering assets are recorded as gas_turbine. Electric drive is not assumed for any terminal.</t>
+          <t>Applying nameplate utilisation here overstates the terminal's emissions roughly thirtyfold</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>saint_john_utilisation</t>
+          <t>lng_energy_content</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.025</v>
+        <v>52</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>MMBtu per tonne</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2847,87 +2847,87 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Actual throughput at the Saint John import terminal. Repsol's annual report records 8 TBtu regasified in 2023 and 10 TBtu in 2022, against 7.5 mtpa of nameplate capacity. Corroborated by the CER, which found the terminal at 4 per cent of send-out capacity in 2017, with cargo counts falling from 42 in 2011 to 5 in 2017.</t>
+          <t>Standard LNG higher heating value, 52 MMBtu per tonne. Equivalent to 54.86 GJ/t (x 1.05506 GJ per MMBtu), which agrees within 0.25% with the 55 MJ/kg HHV used by Balcombe et al. for the figure-10 comparison and by the IEA (2025) LNG supply report. The two figures in this repository are therefore consistent, not conflicting.</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>https://lngprime.com/americas/repsols-saint-john-lng-terminal-to-get-galileos-reliquefaction-tech/115035/</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2023</t>
+          <t>https://iea.blob.core.windows.net/assets/df9b1bed-4e16-4db8-bec5-a5fa117a9130/AssessingemissionsfromLNGsupplyandabatementoptions.pdf</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>Applying nameplate utilisation here overstates the terminal's emissions roughly thirtyfold</t>
+          <t>Used to convert Saint John's reported throughput in TBtu into tonnes. Recorded 3 September 2026; previously an uncited method constant.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>lng_energy_content</t>
+          <t>lng_export_licence_max_term</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MMBtu per tonne</t>
+          <t>years</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>method constant</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Energy content of LNG, used to convert reported throughput in energy units into tonnes.</t>
+          <t>Maximum duration of an LNG export licence under the Canadian Energy Regulator Act, raised from 40 years by Bill C-15, Division 41 of Part 5, royal assent 26 March 2026. No 50 year licence has yet been issued: Cedar's licence, approved January 2026, is for 40 years. Precedent suggests holders will apply to extend, as they did when the ceiling rose from 25 to 40 in 2015.</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>https://www.parl.ca/documentviewer/en/45-1/bill/C-15/royal-assent</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>Also required for the per-kWh energy source comparison</t>
+          <t>Gives the 50 year lifespan sensitivity a legal basis</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>lng_export_licence_max_term</t>
+          <t>canada_2030_overshoot_gap</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>MtCO2e</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>assumption</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Maximum duration of an LNG export licence under the Canadian Energy Regulator Act, raised from 40 years by Bill C-15, Division 41 of Part 5, royal assent 26 March 2026. No 50 year licence has yet been issued: Cedar's licence, approved January 2026, is for 40 years. Precedent suggests holders will apply to extend, as they did when the ceiling rose from 25 to 40 in 2015.</t>
+          <t>Round figure in the neighbourhood of projected 2030 emissions (646 Mt) minus the 417-455 Mt target range (arithmetic interval 191-229). 200 is a judgement, not the difference of two cells.</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>https://www.parl.ca/documentviewer/en/45-1/bill/C-15/royal-assent</t>
+          <t>https://climateactiontracker.org/countries/canada/</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2937,22 +2937,22 @@
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>Gives the 50 year lifespan sensitivity a legal basis</t>
+          <t>Typed assumption. The interval is 191 to 229 Mt.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>canada_2030_overshoot_gap</t>
+          <t>upstream_ch4_share</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>200</v>
+        <v>0.3</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MtCO2e</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2962,113 +2962,113 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Round figure in the neighbourhood of projected 2030 emissions (646 Mt) minus the 417-455 Mt target range (arithmetic interval 191-229). 200 is a judgement, not the difference of two cells.</t>
+          <t>Share of upstream oil and gas emissions that is methane rather than carbon dioxide. Required to apply the measurement correction and the GWP20 uplift to the methane portion only. Canada's 2023 National Inventory Report gives 20 per cent for the oil and gas sector nationally, but that includes oil sands, which are far more carbon dioxide intensive than gas production. British Columbia is gas-dominated, which raises the share, while its 51 per cent methane reduction by 2023 lowers it.</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>https://climateactiontracker.org/countries/canada/</t>
+          <t>https://gazette.gc.ca/rp-pr/p1/2023/2023-12-16/html/reg3-eng.html</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Typed assumption. The interval is 191 to 229 Mt.</t>
+          <t>Tested across 20 to 40 per cent</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>upstream_ch4_share</t>
+          <t>upstream_measurement_correction</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>multiplier</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>assumption</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Share of upstream oil and gas emissions that is methane rather than carbon dioxide. Required to apply the measurement correction and the GWP20 uplift to the methane portion only. Canada's 2023 National Inventory Report gives 20 per cent for the oil and gas sector nationally, but that includes oil sands, which are far more carbon dioxide intensive than gas production. British Columbia is gas-dominated, which raises the share, while its 51 per cent methane reduction by 2023 lowers it.</t>
+          <t>Factor by which peer-reviewed measurement studies find Canadian inventories understate upstream oil and gas methane. Three independent studies agree: 6,650 site measurements across Canada, an Alberta measurement-based inventory, and a British Columbia aircraft survey giving 1.7.</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>https://gazette.gc.ca/rp-pr/p1/2023/2023-12-16/html/reg3-eng.html</t>
+          <t>https://www.nature.com/articles/s41598-021-87610-3</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>Tested across 20 to 40 per cent</t>
+          <t>Applied to the methane portion only</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>upstream_measurement_correction</t>
+          <t>liquefaction_gas_turbine</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.5</v>
+        <v>0.29</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>multiplier</t>
+          <t>tCO2e per t LNG</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Factor by which peer-reviewed measurement studies find Canadian inventories understate upstream oil and gas methane. Three independent studies agree: 6,650 site measurements across Canada, an Alberta measurement-based inventory, and a British Columbia aircraft survey giving 1.7.</t>
+          <t>Liquefaction intensity for gas turbine drive, implied by LNG Canada's environmental assessment of roughly 4 MtCO2e per year against 14 mtpa of capacity.</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>https://www.nature.com/articles/s41598-021-87610-3</t>
+          <t>https://www.projects.eao.gov.bc.ca/p/lng-canada-export-terminal</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>Applied to the methane portion only</t>
+          <t>Equals Emission Factors liquefaction central. Applied to every terminal for its whole operating life as of August 2026.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>liquefaction_gas_turbine</t>
+          <t>liquefaction_electric</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.29</v>
+        <v>0.15</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -3077,38 +3077,33 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Liquefaction intensity for gas turbine drive, implied by LNG Canada's environmental assessment of roughly 4 MtCO2e per year against 14 mtpa of capacity.</t>
+          <t>Pembina Institute, Squaring the Circle: State of LNG 2023, reported intensity for LNG Canada Phase 1 under electric drive. Replaces 0.12 (3 September 2026), which no Pembina document states; 0.12 appears to have been a misreading of the 0.11 tCO2e/t reduction in Wellhead to Waterline (2014) as an absolute level. The same report gives 0.059 for Phase 2 and 0.04 for Woodfibre.</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>https://www.projects.eao.gov.bc.ca/p/lng-canada-export-terminal</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>2015</t>
+          <t>https://www.pembina.org/reports/squaring-the-circle-state-of-lng-2023.pdf</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>Equals Emission Factors liquefaction central. Applied to every terminal for its whole operating life as of August 2026.</t>
+          <t>Figure-8 appendix counterfactual and Emission Factors range_low. NOT used in the central case, which is gas turbine 0.29 for every terminal. BC EAO 0.021 grid / 0.156 gas-barge are a separate SI sensitivity on a facility-total boundary.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>liquefaction_electric</t>
+          <t>bc_lng_emission_intensity_benchmark</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -3117,37 +3112,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>assumption</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Declared assumption. Previously cited as Pembina Institute electrified LNG; no Pembina document stating 0.12 tCO2e/t was located. Retained as the figure-8 counterfactual and Emission Factors range_low. Not used in the central case. EAO 0.021 / 0.156 are a separate SI.</t>
+          <t>Legislated benchmark under British Columbia's Greenhouse Gas Industrial Reporting and Control Act, covering gas entering the facility to loading onto ships. Facilities above it must buy offsets, buy permits from a better-performing facility, or pay into a technology fund.</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>https://www2.gov.bc.ca/gov/content/environment/climate-change/industry/reporting</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2016</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>Pembina Squaring the Circle (2023) uses 0.15 (LNG Canada Phase 1), 0.059 (Phase 2) and 0.04 (Woodfibre), not 0.12. https://www.pembina.org/reports/squaring-the-circle-state-of-lng-2023.pdf</t>
+          <t>A gas turbine facility at 0.29 exceeds this by 0.13, about 1.8 Mt/yr across 14 mtpa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>bc_lng_emission_intensity_benchmark</t>
+          <t>route_bc_to_northeast_asia_nm</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.16</v>
+        <v>3800</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>tCO2e per t LNG</t>
+          <t>nautical miles</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3157,33 +3157,33 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Legislated benchmark under British Columbia's Greenhouse Gas Industrial Reporting and Control Act, covering gas entering the facility to loading onto ships. Facilities above it must buy offsets, buy permits from a better-performing facility, or pay into a technology fund.</t>
+          <t>Oxford Institute for Energy Studies, west coast Canada to Tokyo, as cited by CAPP. Black &amp; Veatch citing PortWorld gives approximately 4,000 nm for the same run.</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>https://www2.gov.bc.ca/gov/content/environment/climate-change/industry/reporting</t>
+          <t>https://www.capp.ca/wp-content/uploads/2026/05/The-Case-for-Canadian-LNG-April-17-2026.pdf</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>A gas turbine facility at 0.29 exceeds this by 0.13, about 1.8 Mt/yr across 14 mtpa</t>
+          <t>One way</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>route_bc_to_northeast_asia_nm</t>
+          <t>route_us_gulf_to_northeast_asia_nm</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3800</v>
+        <v>9200</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -3197,17 +3197,12 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Oxford Institute for Energy Studies, west coast Canada to Tokyo, as cited by CAPP. Black &amp; Veatch citing PortWorld gives approximately 4,000 nm for the same run.</t>
+          <t>US Gulf Coast to Tokyo via the Panama Canal. Reference point only, used to test the industry's proximity claim.</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>https://www.capp.ca/wp-content/uploads/2026/05/The-Case-for-Canadian-LNG-April-17-2026.pdf</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>2026</t>
+          <t>https://www.bv.com/en-US/perspectives/geographic-location-magnifies-advantages-for-north-american-lng-exports</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -3219,15 +3214,15 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>route_us_gulf_to_northeast_asia_nm</t>
+          <t>voyage_days_bc_to_north_asia</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>9200</v>
+        <v>10</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>nautical miles</t>
+          <t>days</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3237,32 +3232,33 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>US Gulf Coast to Tokyo via the Panama Canal. Reference point only, used to test the industry's proximity claim.</t>
+          <t>Reported at the time of LNG Canada's first cargo, against 20 days from the US Gulf Coast via Panama.</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>https://www.bv.com/en-US/perspectives/geographic-location-magnifies-advantages-for-north-american-lng-exports</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>One way</t>
-        </is>
-      </c>
+          <t>https://www.theglobeandmail.com/business/article-lng-canada-liquefied-natural-gas-shipment-asia/</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>voyage_days_bc_to_north_asia</t>
+          <t>ocean_transport_intensity_range_low</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10</v>
+        <v>0.05</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>tCO2e per t LNG delivered</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3272,17 +3268,17 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Reported at the time of LNG Canada's first cargo, against 20 days from the US Gulf Coast via Panama.</t>
+          <t>Peer reviewed supplier-specific LNG lifecycle assessment. Ocean transport ranges from 0.05 tCO2e/t (short routes) to 0.31 (long routes), a sixfold spread, confirming route matters.</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>https://www.theglobeandmail.com/business/article-lng-canada-liquefied-natural-gas-shipment-asia/</t>
+          <t>https://pubs.acs.org/doi/10.1021/acssuschemeng.1c03307</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -3290,11 +3286,11 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ocean_transport_intensity_range_low</t>
+          <t>ocean_transport_intensity_range_high</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.05</v>
+        <v>0.31</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -3308,7 +3304,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Peer reviewed supplier-specific LNG lifecycle assessment. Ocean transport ranges from 0.05 tCO2e/t (short routes) to 0.31 (long routes), a sixfold spread, confirming route matters.</t>
+          <t>Same source. Upper end corresponds to long routes such as US Gulf Coast to Taiwan.</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -3326,51 +3322,55 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ocean_transport_intensity_range_high</t>
+          <t>route_atlantic_routing_factor</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.31</v>
+        <v>1.125</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>tCO2e per t LNG delivered</t>
+          <t>multiplier</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Same source. Upper end corresponds to long routes such as US Gulf Coast to Taiwan.</t>
+          <t>Ratio of actual sailing distance to great circle distance for a North Atlantic crossing. Calibrated on Saint John NB to Rotterdam: SeaRates gives 5,648 km (3,050 nm) against a great circle of 2,712 nm. Applied to Atlantic routes only.</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>https://pubs.acs.org/doi/10.1021/acssuschemeng.1c03307</t>
+          <t>https://www.searates.com/distance-time/</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr"/>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Not applied to Pacific routes</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>route_atlantic_routing_factor</t>
+          <t>route_baie_comeau_to_rotterdam_nm</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1.125</v>
+        <v>2980</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>multiplier</t>
+          <t>nautical miles</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Ratio of actual sailing distance to great circle distance for a North Atlantic crossing. Calibrated on Saint John NB to Rotterdam: SeaRates gives 5,648 km (3,050 nm) against a great circle of 2,712 nm. Applied to Atlantic routes only.</t>
+          <t>Great circle from port coordinates, scaled by the Atlantic routing factor.</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -3395,18 +3395,18 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>Not applied to Pacific routes</t>
+          <t>Estimate, not a published sailing distance</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>route_baie_comeau_to_rotterdam_nm</t>
+          <t>route_fermeuse_to_rotterdam_nm</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2980</v>
+        <v>2470</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -3442,11 +3442,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>route_fermeuse_to_rotterdam_nm</t>
+          <t>route_saint_john_to_rotterdam_nm</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2470</v>
+        <v>3050</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3455,12 +3455,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Great circle from port coordinates, scaled by the Atlantic routing factor.</t>
+          <t>Actual sailing distance, 5,648 km, from the SeaRates port-to-port calculator.</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -3475,22 +3475,22 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>Estimate, not a published sailing distance</t>
+          <t>The calibration point for the Atlantic routing factor</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>route_saint_john_to_rotterdam_nm</t>
+          <t>lng_carrier_aer_gco2_per_dwt_nm</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3050</v>
+        <v>8.5</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>nautical miles</t>
+          <t>gCO2 per DWT per nautical mile</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3500,37 +3500,37 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Actual sailing distance, 5,648 km, from the SeaRates port-to-port calculator.</t>
+          <t>IMO Data Collection System 2023 annual report, LNG carrier fleet average Annual Efficiency Ratio, as reported in an analysis of EU MRV 2023 data. Annual figure, so it already includes ballast legs.</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>https://www.searates.com/distance-time/</t>
+          <t>https://www.mdpi.com/2077-1312/13/8/1437</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>The calibration point for the Atlantic routing factor</t>
+          <t>Use to scale shipping by route distance</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>lng_carrier_aer_gco2_per_dwt_nm</t>
+          <t>lng_carrier_kgco2_per_nm</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>8.5</v>
+        <v>940</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>gCO2 per DWT per nautical mile</t>
+          <t>kg CO2 per nautical mile</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3540,117 +3540,114 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>IMO Data Collection System 2023 annual report, LNG carrier fleet average Annual Efficiency Ratio, as reported in an analysis of EU MRV 2023 data. Annual figure, so it already includes ballast legs.</t>
+          <t>EU JRC analysis of 2019 EU MRV data. LNG carriers are the highest-emitting ship category per nautical mile travelled.</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>https://www.mdpi.com/2077-1312/13/8/1437</t>
+          <t>https://publications.jrc.ec.europa.eu/repository/bitstream/JRC128870/JRC128870_01.pdf</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>Use to scale shipping by route distance</t>
+          <t>Per ship, not per tonne of cargo</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>lng_carrier_kgco2_per_nm</t>
+          <t>lng_carrier_methane_slip_uplift</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>940</v>
+        <v>1.44</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>kg CO2 per nautical mile</t>
+          <t>multiplier</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>derived</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>EU JRC analysis of 2019 EU MRV data. LNG carriers are the highest-emitting ship category per nautical mile travelled.</t>
+          <t>Derived from the first primary measurement study of an LNG carrier voyage, which recorded 68.1 t CH4 against 4,600 t CO2. At GWP100 of 29.8 this raises voyage emissions by about 44 per cent. Methane slip averaged 3.8 per cent across engines.</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>https://publications.jrc.ec.europa.eu/repository/bitstream/JRC128870/JRC128870_01.pdf</t>
+          <t>https://pubs.acs.org/doi/10.1021/acs.est.2c01383</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>Per ship, not per tonne of cargo</t>
+          <t>Applies to the shipping stage only</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>lng_carrier_methane_slip_uplift</t>
+          <t>cargo_tonnes_per_dwt</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1.44</v>
+        <v>0.85</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>multiplier</t>
+          <t>fraction</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>assumption</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Derived from the first primary measurement study of an LNG carrier voyage, which recorded 68.1 t CH4 against 4,600 t CO2. At GWP100 of 29.8 this raises voyage emissions by about 44 per cent. Methane slip averaged 3.8 per cent across engines.</t>
+          <t>Model assumption - typical ratio of LNG cargo tonnes to carrier deadweight. Needed to convert AER, which is per DWT, into emissions per tonne of cargo.</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>https://pubs.acs.org/doi/10.1021/acs.est.2c01383</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>2022</t>
+          <t>Not available</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>Applies to the shipping stage only</t>
+          <t>Sensitivity worth testing</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>cargo_tonnes_per_dwt</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>0.85</v>
+          <t>liquefaction_electrification_assumed</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>fraction</t>
+          <t>category</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3658,71 +3655,77 @@
           <t>assumption</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>Model assumption - typical ratio of LNG cargo tonnes to carrier deadweight. Needed to convert AER, which is per DWT, into emissions per tonne of cargo.</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Model assumption - no external source</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>Not available</t>
         </is>
       </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>Sensitivity worth testing</t>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Electric drive is not assumed for any terminal. Of the projects claiming electrification, only Cedar and Woodfibre have interconnection works under construction; the remainder rest on memoranda of understanding, aspirations conditional on transmission that has not been built, or statements with no firm date. Ksi Lisims holds an MOU with BC Hydro for up to 600 MW conditional on the North Coast Transmission Line expansion, which is not built. LNG Canada Phase 2 states an intention to transition to electric motors as more renewable power becomes available, with no date and no contracted supply. There is not sufficient evidence that electric drive will be in use at these facilities, and a commitment contingent on infrastructure that does not exist is not a basis for lowering the emissions factor. Where electrification is later contracted and built, this assumption should be revisited.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>tmx_oil_lifecycle_per_barrel</t>
+          <t>assumed_first_export_year_if_missing</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.513</v>
+        <v>2030</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>tCO2e/bbl</t>
+          <t>year</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>Sum of tmx_oil_upstream_per_barrel (0.075) + tmx_oil_transport_per_barrel (0.008) + tmx_oil_combustion_per_barrel (0.43). See those rows for sources.</t>
-        </is>
-      </c>
-      <c r="F62" s="4" t="inlineStr">
+          <t>assumption</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Named model parameter: calendar start year filled when Asset Register first_export_year is blank. In-scope assets: tilbury_phase_2, marinvest_baie_comeau, summit_lake_pg_lng, fermeuse_energy_flng, discovery_t1t4, kanata_lng. With licence-end stops, every dated authorised end year is 2056-2066; the published panel tail is entirely this placeholder.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>Not available</t>
         </is>
       </c>
-      <c r="H62" s="4" t="inlineStr">
-        <is>
-          <t>Derived identity. Oil runs at nameplate x 365 x 40 years, unlike LNG. Figure 7 states the utilisation asymmetry. Alberta bitumen is not given its own heavier upstream factor.</t>
+      <c r="G62" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Central value 2030. Sensitivity at 2033 and 2035 is reported. Summit Lake states a 30-year life; the other five use lifecycle_years_default.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>liquefaction_electrification_assumed</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
+          <t>monte_carlo_seed</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>20260828</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3732,7 +3735,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Model assumption - no external source</t>
+          <t>Seed for the decoupled physics Monte Carlo (numpy Generator). Recorded in the run manifest.</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3740,29 +3743,27 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
+      <c r="G63" t="n">
+        <v>2026</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Electric drive is not assumed for any terminal. Of the projects claiming electrification, only Cedar and Woodfibre have interconnection works under construction; the remainder rest on memoranda of understanding, aspirations conditional on transmission that has not been built, or statements with no firm date. Ksi Lisims holds an MOU with BC Hydro for up to 600 MW conditional on the North Coast Transmission Line expansion, which is not built. LNG Canada Phase 2 states an intention to transition to electric motors as more renewable power becomes available, with no date and no contracted supply. There is not sufficient evidence that electric drive will be in use at these facilities, and a commitment contingent on infrastructure that does not exist is not a basis for lowering the emissions factor. Where electrification is later contracted and built, this assumption should be revisited.</t>
+          <t>Do not reuse a draw sequence across published runs without recording a new seed.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>assumed_first_export_year_if_missing</t>
+          <t>monte_carlo_n_draws</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2030</v>
+        <v>10000</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>year</t>
+          <t>count</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3772,7 +3773,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Named model parameter: calendar start year filled when Asset Register first_export_year is blank. In-scope assets: tilbury_phase_2, marinvest_baie_comeau, summit_lake_pg_lng, fermeuse_energy_flng, discovery_t1t4, kanata_lng. With licence-end stops, every dated authorised end year is 2056-2066; the published panel tail is entirely this placeholder.</t>
+          <t>Number of physics draws. Price schedules are applied after, not rebuilt inside the loop.</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3785,22 +3786,24 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Central value 2030. Sensitivity at 2033 and 2035 is reported. Summit Lake states a 30-year life; the other five use lifecycle_years_default.</t>
+          <t>10,000 draws for stable 5th/95th percentiles.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>monte_carlo_seed</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>20260828</v>
+          <t>headline_scope_chains</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>export</t>
+        </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>comma-separated chains</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -3810,7 +3813,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Seed for the decoupled physics Monte Carlo (numpy Generator). Recorded in the run manifest.</t>
+          <t>Model assumption - no external source</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3823,22 +3826,24 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Do not reuse a draw sequence across published runs without recording a new seed.</t>
+          <t>Headline results include assets whose chain is in headline_scope_chains and whose calc_group is in headline_scope_calc_groups. Domestic peak-shaving and other non-export assets are out of headline; they stay in the register. Inventing a 1971/1976 retirement date is not supported.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>monte_carlo_n_draws</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>10000</v>
+          <t>headline_scope_calc_groups</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>operating,under_construction,proposed</t>
+        </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>count</t>
+          <t>comma-separated calc_groups</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3848,7 +3853,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Number of physics draws. Price schedules are applied after, not rebuilt inside the loop.</t>
+          <t>Model assumption - no external source</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3861,98 +3866,98 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>10,000 draws for stable 5th/95th percentiles.</t>
+          <t>Headline results include assets whose chain is in headline_scope_chains and whose calc_group is in headline_scope_calc_groups. Domestic peak-shaving and other non-export assets are out of headline; they stay in the register. Inventing a 1971/1976 retirement date is not supported.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>headline_scope_chains</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>export</t>
-        </is>
+          <t>liquefaction_electric_drive_gas_generation</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.156</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>comma-separated chains</t>
+          <t>tCO2e per t LNG</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>assumption</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Model assumption - no external source</t>
+          <t>British Columbia Environmental Assessment Office, Assessment Report for Ksi Lisims LNG, 7 August 2025, Canadian Impact Assessment Registry document 163192E, pages 847 to 848 - Alternative Case, gas-fired power barges</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v>2026</v>
+          <t>https://iaac-aeic.gc.ca/050/documents/p82797/163192E.pdf</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Headline results include assets whose chain is in headline_scope_chains and whose calc_group is in headline_scope_calc_groups. Domestic peak-shaving and other non-export assets are out of headline; they stay in the register. Inventing a 1971/1976 retirement date is not supported.</t>
+          <t>SENSITIVITY ONLY - the central liquefaction factor stays 0.29 for every terminal. BOUNDARY: this is the facility total intensity including marine sources, not the liquefaction stage alone, so it is not like for like with the 0.29 liquefaction factor on the Emission Factors sheet. Any comparison against 0.29 is therefore approximate and is labelled as such wherever it is reported.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>headline_scope_calc_groups</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>operating,under_construction,proposed</t>
-        </is>
+          <t>liquefaction_electric_drive_grid</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0.021</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>comma-separated calc_groups</t>
+          <t>tCO2e per t LNG</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>assumption</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Model assumption - no external source</t>
+          <t>British Columbia Environmental Assessment Office, Assessment Report for Ksi Lisims LNG, 7 August 2025, Canadian Impact Assessment Registry document 163192E, pages 847 to 848 - Base Case, grid supply</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G68" t="n">
-        <v>2026</v>
+          <t>https://iaac-aeic.gc.ca/050/documents/p82797/163192E.pdf</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Headline results include assets whose chain is in headline_scope_chains and whose calc_group is in headline_scope_calc_groups. Domestic peak-shaving and other non-export assets are out of headline; they stay in the register. Inventing a 1971/1976 retirement date is not supported.</t>
+          <t>SENSITIVITY ONLY - the central liquefaction factor stays 0.29 for every terminal. BOUNDARY: this is the facility total intensity including marine sources, not the liquefaction stage alone, so it is not like for like with the 0.29 liquefaction factor on the Emission Factors sheet. Any comparison against 0.29 is therefore approximate and is labelled as such wherever it is reported.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>liquefaction_electric_drive_gas_generation</t>
+          <t>lca_howarth_gwp20_low</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.156</v>
+        <v>7.37</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3966,33 +3971,33 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>British Columbia Environmental Assessment Office, Assessment Report for Ksi Lisims LNG, 7 August 2025, Canadian Impact Assessment Registry document 163192E, pages 847 to 848 - Alternative Case, gas-fired power barges</t>
+          <t>Howarth 2024, Energy Science &amp; Engineering, Table 3, GWP20, average 38-day voyage.</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://iaac-aeic.gc.ca/050/documents/p82797/163192E.pdf</t>
+          <t>https://doi.org/10.1002/ese3.1934</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>SENSITIVITY ONLY - the central liquefaction factor stays 0.29 for every terminal. BOUNDARY: this is the facility total intensity including marine sources, not the liquefaction stage alone, so it is not like for like with the 0.29 liquefaction factor on the Emission Factors sheet. Any comparison against 0.29 is therefore approximate and is labelled as such wherever it is reported.</t>
+          <t>Figure 10 only. Not mixed with this model's GWP100 totals.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>liquefaction_electric_drive_grid</t>
+          <t>lca_howarth_gwp20_high</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.021</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -4006,37 +4011,37 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>British Columbia Environmental Assessment Office, Assessment Report for Ksi Lisims LNG, 7 August 2025, Canadian Impact Assessment Registry document 163192E, pages 847 to 848 - Base Case, grid supply</t>
+          <t>Howarth 2024 Table 3, GWP20 upper end of the four tanker types.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://iaac-aeic.gc.ca/050/documents/p82797/163192E.pdf</t>
+          <t>https://doi.org/10.1002/ese3.1934</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>SENSITIVITY ONLY - the central liquefaction factor stays 0.29 for every terminal. BOUNDARY: this is the facility total intensity including marine sources, not the liquefaction stage alone, so it is not like for like with the 0.29 liquefaction factor on the Emission Factors sheet. Any comparison against 0.29 is therefore approximate and is labelled as such wherever it is reported.</t>
+          <t>Figure 10 only.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>tmx_oil_upstream_per_barrel</t>
+          <t>lca_roman_white_w2r_p025</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.075</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>tCO2e/bbl</t>
+          <t>tCO2e per t LNG</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4046,12 +4051,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Natural Resources Canada, Roadmap for the Decarbonization of Canada's Oil and Gas Sector: 2021 oil sands production intensity approximately 75 kg CO2e/barrel. Slate: Canadian oil sands average, not a TMX ticket-by-ticket mix. TMX also carries conventional crude (NRCan ~48-49 kg/bbl), so 0.075 is oil-sands-heavy for the TMX mix.</t>
+          <t>Roman-White et al. 2021, ACS Sustainable Chemistry &amp; Engineering, Table 1, China, GWP100, cradle to regasification, P2.5.</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://natural-resources.canada.ca/climate-change/roadmap-decarbonization-canada-s-oil-gas-sector</t>
+          <t>https://doi.org/10.1021/acssuschemeng.1c03307</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4061,57 +4066,62 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Upstream production only. Not well-to-tank.</t>
+          <t>Figure 10 only.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>tmx_oil_transport_per_barrel</t>
+          <t>lca_roman_white_w2r_expected</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.008</v>
+        <v>1.19</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>tCO2e/bbl</t>
+          <t>tCO2e per t LNG</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>assumption</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Declared assumption. 8 kgCO2e/bbl for pipeline transport. No document stating this figure for TMX was located.</t>
+          <t>Roman-White et al. 2021 Table 1 expected value, not an arithmetic midpoint.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>https://doi.org/10.1021/acssuschemeng.1c03307</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2021</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Not a cited TMX intensity.</t>
+          <t>Figure 10 only.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>tmx_oil_combustion_per_barrel</t>
+          <t>lca_roman_white_w2r_p975</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.43</v>
+        <v>1.51</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>tCO2e/bbl</t>
+          <t>tCO2e per t LNG</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4121,112 +4131,117 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>IPCC 2006 Guidelines, Volume 2, Chapter 1: crude oil default NCV 42.3 TJ/Gg (Table 1.2) and carbon content 20.0 kg C/GJ (Table 1.3) give 0.423 tCO2/bbl at 100% oxidation; stored as 0.43. Slate: IPCC generic crude, not a WCSB or TMX assay.</t>
+          <t>Roman-White et al. 2021 Table 1, P97.5.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://www.ipcc-nggip.iges.or.jp/public/2006gl/pdf/2_Volume2/V2_1_Ch1_Introduction.pdf</t>
+          <t>https://doi.org/10.1021/acssuschemeng.1c03307</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Combustion CO2 only. Rounding 0.423 to 0.43 is undeclared at the third decimal.</t>
+          <t>Figure 10 only.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>tmx_expansion_bpd</t>
+          <t>lca_balcombe_lng_stages_low_g_per_mj_hhv</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>590000</v>
+        <v>11.2</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>barrels per day</t>
+          <t>gCO2e per MJ HHV</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Increment implied by the expanded-system 890,000 bpd less the pre-expansion ~300,000 bpd, both stated in Trans Mountain's description of the May 2024 expansion.</t>
+          <t>Balcombe et al. 2016 literature range, liquefaction + tanker + regasification.</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://www.transmountain.com/news/trans-mountain-pipeline-system-a-strategic-canadian-asset</t>
+          <t>https://doi.org/10.1002/ese3.161</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>890,000 - 300,000 = 590,000. Figure 7 expansion-only bar.</t>
+          <t>Figure 10. Converted with lca_hhv_mj_per_kg.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>days_per_year</t>
+          <t>lca_balcombe_lng_stages_high_g_per_mj_hhv</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>365</v>
+        <v>31.1</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>gCO2e per MJ HHV</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>method constant</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Civil year used to convert barrels per day to an annual total for the oil comparator. Not a leap-year correction.</t>
+          <t>Balcombe et al. 2016 literature range, upper end.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>https://doi.org/10.1002/ese3.161</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2016</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Structural method constant. LNG utilisation is a fraction of nameplate, not a day count.</t>
+          <t>Figure 10.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>lca_howarth_gwp20_low</t>
+          <t>lca_hhv_mj_per_kg</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>7.37</v>
+        <v>55</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>tCO2e per t LNG</t>
+          <t>MJ per kg</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4236,342 +4251,62 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Howarth 2024, Energy Science &amp; Engineering, Table 3, GWP20, average 38-day voyage.</t>
+          <t>Higher heating value used by Balcombe et al. to report LNG-stage intensities. Not this model's lng_energy_content (52).</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/ese3.1934</t>
+          <t>https://doi.org/10.1002/ese3.161</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Figure 10 only. Not mixed with this model's GWP100 totals.</t>
+          <t>Figure 10 conversion only.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>lca_howarth_gwp20_high</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>8.029999999999999</v>
+          <t>placeholder_sensitivity_years</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2033,2035</t>
+        </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>tCO2e per t LNG</t>
+          <t>years</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>cited</t>
+          <t>assumption</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Howarth 2024 Table 3, GWP20 upper end of the four tanker types.</t>
+          <t>Sensitivity start years for assets with a blank first_export_year. Central remains assumed_first_export_year_if_missing (2030). These years are not filed dates.</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/ese3.1934</t>
+          <t>Not available</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
-        <is>
-          <t>Figure 10 only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>lca_roman_white_w2r_p025</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>tCO2e per t LNG</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>Roman-White et al. 2021, ACS Sustainable Chemistry &amp; Engineering, Table 1, China, GWP100, cradle to regasification, P2.5.</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1021/acssuschemeng.1c03307</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Figure 10 only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>lca_roman_white_w2r_expected</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>tCO2e per t LNG</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Roman-White et al. 2021 Table 1 expected value, not an arithmetic midpoint.</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1021/acssuschemeng.1c03307</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Figure 10 only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>lca_roman_white_w2r_p975</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>tCO2e per t LNG</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Roman-White et al. 2021 Table 1, P97.5.</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1021/acssuschemeng.1c03307</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Figure 10 only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>lca_balcombe_lng_stages_low_g_per_mj_hhv</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>gCO2e per MJ HHV</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Balcombe et al. 2016 literature range, liquefaction + tanker + regasification.</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/ese3.161</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Figure 10. Converted with lca_hhv_mj_per_kg.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>lca_balcombe_lng_stages_high_g_per_mj_hhv</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>gCO2e per MJ HHV</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>Balcombe et al. 2016 literature range, upper end.</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/ese3.161</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>Figure 10.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>lca_hhv_mj_per_kg</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>55</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>MJ per kg</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>cited</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>Higher heating value used by Balcombe et al. to report LNG-stage intensities. Not this model's lng_energy_content (52).</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/ese3.161</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Figure 10 conversion only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>placeholder_sensitivity_years</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>2033,2035</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>assumption</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Sensitivity start years for assets with a blank first_export_year. Central remains assumed_first_export_year_if_missing (2030). These years are not filed dates.</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
         <is>
           <t>SI only. Do not treat as filed first-export years.</t>
         </is>

--- a/Inputs/Canada_LNG_Data_Inputs.xlsx
+++ b/Inputs/Canada_LNG_Data_Inputs.xlsx
@@ -1193,27 +1193,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.1</v>
+        <v>0.074</v>
       </c>
       <c r="F3" t="n">
-        <v>0.05</v>
+        <v>0.037</v>
       </c>
       <c r="G3" t="n">
-        <v>0.18</v>
+        <v>0.133</v>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>Assumed 0.10 tCO2e per t LNG. No ICF or Sphera document stating this figure was located. The BC Environmental Assessment Office Coastal GasLink assessment (October 2014) reports 3.517 MtCO2e/yr at 5 Bcf/d design capacity. Scaled to the 2.1 Bcf/d serving LNG Canada Phase 1 that implies 1.48 MtCO2e/yr against this model's 1.47 at 0.10 t/t. That check confirms the arithmetic of scaling the assumed factor, not an independent measurement of 0.10.</t>
+          <t>0.074 tCO2e per t LNG, from two independent routes that converge. ROUTE A (central): Liu, R.E., Ravikumar, A.P., Bi, X.T., Zhang, S., Nie, Y., Brandt, A., Bergerson, J.A. (2021), 'Greenhouse Gas Emissions of Western Canadian Natural Gas: Proposed Emissions Tracking for Life Cycle Modeling', Environmental Science &amp; Technology 55(14): 9711-9720, https://doi.org/10.1021/acs.est.0c06353 (open PDF https://ngi.stanford.edu/sites/ngi/files/media/file/acs.est_.0c06353.pdf). Results, p. 9713: 'The company emissions intensities using both mass and energy allocation are 4.2 gCO2e/MJ NG at transmission pipeline outlet.' Modern West Advisory for Emissions Reduction Alberta (2022), Life-Cycle Analysis of Canadian Natural Gas: A Pilot Study, section 5.3 p. 43, https://www.eralberta.ca/wp-content/uploads/2022/04/Modern-West-Advisory-Final-Outcomes-Report-Non-Confidential.pdf , restates that same study on the plant-exit boundary: 'If the transmission emissions are excluded to make the boundaries consistent with the present report, the estimated emission intensity at NG plant exit is approximately 2.86 gCO2e/MJ NG.' The difference is the transmission stage: 4.20 - 2.86 = 1.34 gCO2e/MJ. At lng_energy_content 52 MMBtu/t = 54.863 GJ/t that is 0.0735 tCO2e per t LNG. ROUTE B (independent cross-check, not the central): CER Market Snapshot, 'Greening Canada's pipeline infrastructure' (2022), https://www.cer-rec.gc.ca/en/data-analysis/energy-markets/market-snapshots/2022/market-snapshot-greening-canadas-pipeline-infrastructure.html : 'In 2019, emissions resulting from pipeline transport, primarily emissions related to combustion at compressor stations, accounted for 8.3 MT CO2e', attributed to ECCC National Inventory Report 1990-2019 Part 1 Table 2-5. Over roughly 170 bcm of Canadian marketable gas at 36 PJ/bcm: 8.3 Mt / 6,120 PJ = 1.356 gCO2e/MJ = 0.0744 tCO2e/t. The two routes agree to within 1.2 per cent. Stored as 0.074. Replaces an assumed 0.10 (3 September 2026), which was about 35 per cent above both routes and which no ICF or Sphera document supported. CAVEATS ON ROUTE A. Liu et al. is a case study of Seven Generations Energy's Kakwa operations in Alberta - one operator running relatively new facilities, so plausibly better than the Western Canadian average; the paper's own comparison puts BC estimates at 6.2-12 gCO2e/MJ upstream against its 4.2. The paper's Table 1 Section D gives the modelled transmission pipeline length as 1,100 km (company data; US default 971 km). NOTE THE ABSTRACT SAYS 3.1-4.0 gCO2e/MJ while the Results text says 4.2 for mass and energy allocation and 3.1 / 3.3 for financial and condensate-displacement allocation; the 4.2 used here is the Results figure on the allocation basis this model uses. DISTANCE. This model applies the pipeline factor FLAT, with no distance scaling, unlike shipping. Route A is calibrated on 1,100 km and Route B is a national average haul, while the in-scope feedgas lines are Coastal GasLink 670 km, Prince Rupert Gas Transmission 750 km and FortisBC Eagle Mountain 47 km. If transmission emissions scale with distance, 0.074 is high for every one of them - Woodfibre most of all. That is a stated limitation, not a correction applied here. The Coastal GasLink check (model 1.47 against 1.48 MtCO2e/yr implied by the 2014 BC EAO assessment) confirms the arithmetic of scaling a factor with throughput; it is not an independent measurement of the factor.</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Range 0.05-0.18 is an assumed literature band, not a cited interval. Consistency check: BC EAO 2014 Coastal GasLink Assessment Report, https://projects.eao.gov.bc.ca/api/document/58868fd3e036fb0105768772/fetch/Assessment%20Report%20and%20Appendices%20for%20the%20CGL%20Project%20dated%20October%202014..pdf</t>
+          <t>ASSUMPTION, DECLARED. The 0.037-0.133 band is not cited. It preserves the relative width of the retired 0.05-0.18 band (x0.5 / x1.8) around the new 0.074 central, because no published uncertainty interval for Canadian gas transmission intensity was located. 'Regional greenhouse gas analysis of compressor drivers in natural gas transmission systems in Canada', Journal of Cleaner Production (2023), doi 10.1016/j.jclepro.2023.137150, was the candidate for a structured band but is paywalled and could not be read. The two central routes agreeing to 1.2 per cent (0.0735 and 0.0744) is convergence on the CENTRAL and must not be read as the uncertainty: the real spread is driven by route length and compressor drive type, neither of which this model varies. Do not narrow the Monte Carlo band to the gap between the two routes; that would assert a precision the evidence does not support.</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>Small share of the total, about 3 per cent. Modelled proportional to throughput, whereas compressor stations have a fixed operating baseline regardless of flow.</t>
+          <t>About 2 per cent of the lifecycle total after the move to 0.074. Modelled proportional to throughput and flat in distance, whereas compressor stations have a fixed operating baseline and their fuel burn scales with haul length. The in-scope lines are shorter than the 1,100 km behind Route A, so the factor is more likely high than low for these assets.</t>
         </is>
       </c>
     </row>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Share of upstream oil and gas emissions that is methane rather than carbon dioxide. Required to apply the measurement correction and the GWP20 uplift to the methane portion only. Canada's 2023 National Inventory Report gives 20 per cent for the oil and gas sector nationally, but that includes oil sands, which are far more carbon dioxide intensive than gas production. British Columbia is gas-dominated, which raises the share, while its 51 per cent methane reduction by 2023 lowers it.</t>
+          <t>Share of upstream oil and gas emissions that is methane rather than carbon dioxide. Required to apply the measurement correction and the GWP20 uplift to the methane portion only. ASSUMPTION, DECLARED - 0.30 is not a cited figure. It is now bracketed by a derivation from Johnson, Conrad &amp; Tyner (2023), Communications Earth &amp; Environment, https://doi.org/10.1038/s43247-023-00769-7 , which reports for British Columbia in 2021: total measurement-based upstream oil and gas methane of 144.5 kt/y; an upstream methane intensity of marketed natural gas of 0.38% (95% CI 0.33-0.44%, SI section S3); and that this measurement-based inventory is nominally 1.7 times the official ECCC bottom-up figure (range 1.5-2.0). ROUTE 1, intensity: dividing 0.38% by 1.7 gives an official-basis intensity of 0.224%; per tonne of marketed gas that is 0.00224 t CH4, which at GWP100 29.8 is 0.0666 tCO2e, or 30.3% of the 0.22 inventory_as_reported upstream factor. ROUTE 2, absolute: 144.5 / 1.7 = 85.0 kt CH4 official basis = 2.53 MtCO2e at 29.8; the 0.22 factor over 63 bcm (45.7 Mt LNG-equivalent at 1.38 bcm per mtpa) implies 10.04 MtCO2e of upstream emissions net of transmission, so the share is 25.2%. BRACKET: across the 1.5-2.0 correction range and AR5 (25) versus AR6 (29.8) methane GWP vintages, the two routes span roughly 18% to 34% and centre near 25%. The derivation therefore CORROBORATES 0.30 as being within range while suggesting it sits high. It does not pin the value, so 0.30 is retained and stays typed assumption.</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>https://gazette.gc.ca/rp-pr/p1/2023/2023-12-16/html/reg3-eng.html</t>
+          <t>https://doi.org/10.1038/s43247-023-00769-7</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Tested across 20 to 40 per cent</t>
+          <t>DO NOT substitute the national fugitives share. ECCC's 2026 executive summary reports 46 MtCO2e of oil and gas fugitive methane within roughly 66 MtCO2e of total Fugitive Sources, a share near 70%. This model's upstream stage covers production and processing in total, INCLUDING stationary combustion and flaring, which are nearly all CO2. Applying a fugitives-only share here would overstate methane by roughly a factor of two. Canada's NIR gives about 20% for the oil and gas sector nationally, but that includes oil sands, which are far more CO2-intensive than gas production. SENSITIVITY OF THE MODEL TO THIS VALUE: the central upstream factor is insensitive - 0.22 x (1 - s + 1.5s) gives 0.2530 at s=0.30 and 0.2475 at s=0.25, both rounding to 0.25 - and measurement_high likewise rounds to 0.26 either way. What moves is the near_term_methane_gwp20 scenario (0.428 at s=0.30 against 0.393 at s=0.25) and the CO2/CH4 split in the physics, which flows into the SC-CH4 damages line. OTHER ROUTES ATTEMPTED 3 September 2026 and not closed: the ECCC National Inventory Report Part 3 provincial tables (category 1.B.2 for British Columbia) exist but are served through a JavaScript data-mart portal rather than a direct download, so the CO2/CH4 cells could not be pulled; the UNFCCC Common Reporting Tables for Canada are the route that would work. The BC Provincial Inventory methodology report confirms upstream fugitives are Tier 3 bottom-up facility by facility, so the underlying data distinguishes gases even though the published provincial tables are CO2e only.</t>
         </is>
       </c>
     </row>

--- a/Inputs/Canada_LNG_Data_Inputs.xlsx
+++ b/Inputs/Canada_LNG_Data_Inputs.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>Route-specific range from a peer-reviewed supplier-specific lifecycle assessment: ocean transport runs 0.05 tCO2e/t on short routes to 0.31 on long ones, https://pubs.acs.org/doi/10.1021/acssuschemeng.1c03307. Methane slip measurement: https://pubs.acs.org/doi/10.1021/acs.est.2c01383</t>
+          <t>Route-specific range from a peer-reviewed supplier-specific lifecycle assessment: ocean transport runs 0.05 tCO2e/t on short routes to 0.31 on long ones, https://pubs.acs.org/doi/10.1021/acssuschemeng.1c03307 . Methane slip measurement: https://pubs.acs.org/doi/10.1021/acs.est.2c01383 . WHY THIS MODEL HOLDS 0.12 AGAINST THE IEA'S 0.18. IEA (2025), Assessing Emissions from LNG Supply and Abatement Options, p. 15, gives about 3.5 gCO2e/MJ globally and 3.3 gCO2e/MJ for LNG delivered to China, which at 55 MJ/kg is 0.19 and 0.18 tCO2e/t (https://iea.blob.core.windows.net/assets/df9b1bed-4e16-4db8-bec5-a5fa117a9130/AssessingemissionsfromLNGsupplyandabatementoptions.pdf). That is higher than this model's 0.12, and a reviewer will meet it. Four reasons it is NOT like-for-like: (1) DISTANCE - the IEA average round trip is 10,000 km, against the 14,075 km round trip (7,600 nm) this model uses for the British Columbia to north-east Asia basis, so the IEA figure is for a SHORTER voyage; (2) FLEET AVERAGE, NOT ROUTE - it averages about 7,000 round trips in 2024 across the world fleet, including Arctic ice-class voyages such as Yamal to China, rather than describing any single route; (3) GWP BASIS - the IEA takes 1 t methane as 30 t CO2, against this model's 29.8, and its methane-slip treatment is fleet-wide rather than the measured 1.44 uplift used here; (4) ORIGIN-BLENDED - 'to China' blends US Gulf, Qatari, Australian and Russian origins, so it carries voyages this model does not run. THE HONEST STATEMENT OF THE GAP: per kilometre the IEA implies roughly 2.3 times this model's intensity. That is the real disagreement and it is not resolved by the boundary differences above. The 0.12 is retained because it is Howarth's figure independently reconstructed from IMO Data Collection System fleet data on the voyage this model actually runs - 8.50 gCO2 per DWT per nautical mile over a 7,600 nm round trip, converted to cargo tonnes and uplifted 44 per cent for measured methane slip, giving 0.110 against the stored 0.120. A route-specific derivation on our own voyage is preferred to a fleet average on a different one. Recorded 3 September 2026; see also Outputs/benchmark_comparison.csv.</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1773,15 +1773,19 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Planning range - no published empirical average for BC proposal to FID timelines</t>
+          <t>Lower bound of the FID-delay triangle. Set to 4 years, the bottom of the IEA's stated 4-to-5 year FID-to-completion range: a project is not credibly faster than the fastest observed average. IEA, Global LNG Capacity Tracker: 'the long time lag of 4 to 5 years, on average, between project FID and completion' (https://www.iea.org/data-and-statistics/data-tools/global-lng-capacity-tracker). Rogers, H. (2017), The Forthcoming LNG Supply Wave: A Case of 'Crying Wolf'?, Oxford Institute for Energy Studies, Energy Insight 4, February 2017, page 1: 'Note that the time from FID to project completion is typically 5 years, before unforeseen slippage' (https://www.oxfordenergy.org/wpcms/wp-content/uploads/2017/02/The-Forthcoming-LNG-Supply-Wave-OIES-Energy-Insight.pdf). THE BAND IS ASYMMETRIC ON PURPOSE. 'Before unforeseen slippage' makes 5 years a central that slippage moves in one direction only: LNG projects run late, not early. The OIES sentence appears in a list of factors explaining why 2004-2009 LNG capacity forecasts overshot what was delivered. The retired symmetric 3/5/7 implied a project was as likely to be two years early as two years late, which neither source supports and which the Australian and US project record contradicts. 4/5/8 keeps the cited mid, pulls the optimistic tail in to the bottom of the IEA's own 4-to-5 range, and lets the pessimistic tail run a year further.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr"/>
+          <t>https://www.iea.org/data-and-statistics/data-tools/global-lng-capacity-tracker</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Was 3 (assumed). Raised 3 September 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1804,15 +1808,19 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Planning range, default</t>
+          <t>Delay applied to assets without a confirmed FID, sitting inside the lifespan window rather than extending it. Value unchanged; now carries two independent citations. IEA, Global LNG Capacity Tracker: 'the long time lag of 4 to 5 years, on average, between project FID and completion' (https://www.iea.org/data-and-statistics/data-tools/global-lng-capacity-tracker). Rogers, H. (2017), The Forthcoming LNG Supply Wave: A Case of 'Crying Wolf'?, Oxford Institute for Energy Studies, Energy Insight 4, February 2017, page 1: 'Note that the time from FID to project completion is typically 5 years, before unforeseen slippage' (https://www.oxfordenergy.org/wpcms/wp-content/uploads/2017/02/The-Forthcoming-LNG-Supply-Wave-OIES-Energy-Insight.pdf). THE BAND IS ASYMMETRIC ON PURPOSE. 'Before unforeseen slippage' makes 5 years a central that slippage moves in one direction only: LNG projects run late, not early. The OIES sentence appears in a list of factors explaining why 2004-2009 LNG capacity forecasts overshot what was delivered. The retired symmetric 3/5/7 implied a project was as likely to be two years early as two years late, which neither source supports and which the Australian and US project record contradicts. 4/5/8 keeps the cited mid, pulls the optimistic tail in to the bottom of the IEA's own 4-to-5 range, and lets the pessimistic tail run a year further.</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr"/>
+          <t>https://www.oxfordenergy.org/wpcms/wp-content/uploads/2017/02/The-Forthcoming-LNG-Supply-Wave-OIES-Energy-Insight.pdf</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Unchanged at 5, so the central case is untouched by the 3 September 2026 band change. Applied to the seven proposed assets without FID. post_fid_to_completion = 4.5 rests on the same IEA statement and is reference-only; this row is the one the model reads.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1821,7 +1829,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1835,15 +1843,19 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Planning range</t>
+          <t>Upper bound of the FID-delay triangle. Set to 8 years, three years beyond the cited typical 5, to carry the 'unforeseen slippage' the OIES source names explicitly. IEA, Global LNG Capacity Tracker: 'the long time lag of 4 to 5 years, on average, between project FID and completion' (https://www.iea.org/data-and-statistics/data-tools/global-lng-capacity-tracker). Rogers, H. (2017), The Forthcoming LNG Supply Wave: A Case of 'Crying Wolf'?, Oxford Institute for Energy Studies, Energy Insight 4, February 2017, page 1: 'Note that the time from FID to project completion is typically 5 years, before unforeseen slippage' (https://www.oxfordenergy.org/wpcms/wp-content/uploads/2017/02/The-Forthcoming-LNG-Supply-Wave-OIES-Energy-Insight.pdf). THE BAND IS ASYMMETRIC ON PURPOSE. 'Before unforeseen slippage' makes 5 years a central that slippage moves in one direction only: LNG projects run late, not early. The OIES sentence appears in a list of factors explaining why 2004-2009 LNG capacity forecasts overshot what was delivered. The retired symmetric 3/5/7 implied a project was as likely to be two years early as two years late, which neither source supports and which the Australian and US project record contradicts. 4/5/8 keeps the cited mid, pulls the optimistic tail in to the bottom of the IEA's own 4-to-5 range, and lets the pessimistic tail run a year further.</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr"/>
+          <t>https://www.oxfordenergy.org/wpcms/wp-content/uploads/2017/02/The-Forthcoming-LNG-Supply-Wave-OIES-Energy-Insight.pdf</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Was 7 (assumed, symmetric). Raised 3 September 2026.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1866,7 +1878,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>IEA Global LNG Capacity Tracker - 4 to 5 year global average FID to completion</t>
+          <t>REFERENCE ONLY - read by no module. Retained because it records the same IEA statement that supports fid_delay_mid: 'the long time lag of 4 to 5 years, on average, between project FID and completion' (https://www.iea.org/data-and-statistics/data-tools/global-lng-capacity-tracker). The model applies fid_delay_mid = 5 rather than this row; the two are not independent facts and must not be cited as if they were.</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1881,7 +1893,7 @@
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Documented, not used in the utilisation calculation</t>
+          <t>Marked reference-only 3 September 2026 so the workbook does not carry two disconnected versions of one fact. Do not wire this into the utilisation calculation without retiring fid_delay_mid.</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2667,7 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>https://www.lngcanada.ca/</t>
+          <t>https://www.theglobeandmail.com/business/article-lng-canada-exports-asia-natural-gas-strait-of-hormuz/</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2665,7 +2677,7 @@
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>Replaces year_1_utilisation for this project only</t>
+          <t>OBSERVED DATA AS AT JUNE 2026, recorded 3 September 2026 so this assumption is testable rather than merely asserted. The model still uses the assumed ramp; nothing below has been fed back into it. First cargo 30 June 2025 from Train 1; Train 2 entered production November 2025 (GEM, LNG Canada Terminal page, last edited 18 August 2026, https://www.gem.wiki/LNG_Canada_Terminal ; Norton Rose Fulbright, Canadian LNG industry: 2026 outlook). Vessel departures 4 in December 2025, 10 in January 2026 and 11 in February 2026 (Kpler, via Globe and Mail, 18 March 2026, https://www.theglobeandmail.com/business/article-lng-canada-exports-asia-natural-gas-strait-of-hormuz/ ). Approximately 4.6 Mt exported between June 2025 and mid-March 2026 (RBC Capital Markets, Michael Harvey, same article). 60th cargo mid-March 2026 and approximately 80 cargoes by early May 2026 (EnergyNow, June 2026). April 2026 was the first month above 1 Mt, and production reached 1.2 Mt per month by May 2026. WHAT THE DATA SAYS ABOUT THE ASSUMPTION: against 14 mtpa nameplate, calendar 2025 ran at roughly 11 per cent of a full year against the assumed year-one 25 per cent, while April and May 2026 ran at about 86 and 103 per cent of nameplate against the assumed year-two 60 per cent. THE AVERAGE IS ABOUT RIGHT; THE SHAPE IS NOT. The model starts too high and ramps too slowly, and the two errors largely offset over the life. Retained as a known limitation rather than corrected, because a single-facility observed profile is not a basis for the generic ramp applied to every other asset.</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2707,7 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>https://www.lngcanada.ca/</t>
+          <t>https://www.theglobeandmail.com/business/article-lng-canada-exports-asia-natural-gas-strait-of-hormuz/</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2705,7 +2717,7 @@
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>Replaces year_2_utilisation for this project only</t>
+          <t>OBSERVED DATA AS AT JUNE 2026, recorded 3 September 2026 so this assumption is testable rather than merely asserted. The model still uses the assumed ramp; nothing below has been fed back into it. First cargo 30 June 2025 from Train 1; Train 2 entered production November 2025 (GEM, LNG Canada Terminal page, last edited 18 August 2026, https://www.gem.wiki/LNG_Canada_Terminal ; Norton Rose Fulbright, Canadian LNG industry: 2026 outlook). Vessel departures 4 in December 2025, 10 in January 2026 and 11 in February 2026 (Kpler, via Globe and Mail, 18 March 2026, https://www.theglobeandmail.com/business/article-lng-canada-exports-asia-natural-gas-strait-of-hormuz/ ). Approximately 4.6 Mt exported between June 2025 and mid-March 2026 (RBC Capital Markets, Michael Harvey, same article). 60th cargo mid-March 2026 and approximately 80 cargoes by early May 2026 (EnergyNow, June 2026). April 2026 was the first month above 1 Mt, and production reached 1.2 Mt per month by May 2026. WHAT THE DATA SAYS ABOUT THE ASSUMPTION: against 14 mtpa nameplate, calendar 2025 ran at roughly 11 per cent of a full year against the assumed year-one 25 per cent, while April and May 2026 ran at about 86 and 103 per cent of nameplate against the assumed year-two 60 per cent. THE AVERAGE IS ABOUT RIGHT; THE SHAPE IS NOT. The model starts too high and ramps too slowly, and the two errors largely offset over the life. Retained as a known limitation rather than corrected, because a single-facility observed profile is not a basis for the generic ramp applied to every other asset.</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2747,7 @@
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>https://www.lngcanada.ca/</t>
+          <t>https://www.theglobeandmail.com/business/article-lng-canada-exports-asia-natural-gas-strait-of-hormuz/</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2745,7 +2757,7 @@
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>Replaces steady_state_utilisation for this project only</t>
+          <t>OBSERVED DATA AS AT JUNE 2026, recorded 3 September 2026 so this assumption is testable rather than merely asserted. The model still uses the assumed ramp; nothing below has been fed back into it. First cargo 30 June 2025 from Train 1; Train 2 entered production November 2025 (GEM, LNG Canada Terminal page, last edited 18 August 2026, https://www.gem.wiki/LNG_Canada_Terminal ; Norton Rose Fulbright, Canadian LNG industry: 2026 outlook). Vessel departures 4 in December 2025, 10 in January 2026 and 11 in February 2026 (Kpler, via Globe and Mail, 18 March 2026, https://www.theglobeandmail.com/business/article-lng-canada-exports-asia-natural-gas-strait-of-hormuz/ ). Approximately 4.6 Mt exported between June 2025 and mid-March 2026 (RBC Capital Markets, Michael Harvey, same article). 60th cargo mid-March 2026 and approximately 80 cargoes by early May 2026 (EnergyNow, June 2026). April 2026 was the first month above 1 Mt, and production reached 1.2 Mt per month by May 2026. WHAT THE DATA SAYS ABOUT THE ASSUMPTION: against 14 mtpa nameplate, calendar 2025 ran at roughly 11 per cent of a full year against the assumed year-one 25 per cent, while April and May 2026 ran at about 86 and 103 per cent of nameplate against the assumed year-two 60 per cent. THE AVERAGE IS ABOUT RIGHT; THE SHAPE IS NOT. The model starts too high and ramps too slowly, and the two errors largely offset over the life. Retained as a known limitation rather than corrected, because a single-facility observed profile is not a basis for the generic ramp applied to every other asset.</t>
         </is>
       </c>
     </row>
@@ -2948,7 +2960,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2962,7 +2974,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Share of upstream oil and gas emissions that is methane rather than carbon dioxide. Required to apply the measurement correction and the GWP20 uplift to the methane portion only. ASSUMPTION, DECLARED - 0.30 is not a cited figure. It is now bracketed by a derivation from Johnson, Conrad &amp; Tyner (2023), Communications Earth &amp; Environment, https://doi.org/10.1038/s43247-023-00769-7 , which reports for British Columbia in 2021: total measurement-based upstream oil and gas methane of 144.5 kt/y; an upstream methane intensity of marketed natural gas of 0.38% (95% CI 0.33-0.44%, SI section S3); and that this measurement-based inventory is nominally 1.7 times the official ECCC bottom-up figure (range 1.5-2.0). ROUTE 1, intensity: dividing 0.38% by 1.7 gives an official-basis intensity of 0.224%; per tonne of marketed gas that is 0.00224 t CH4, which at GWP100 29.8 is 0.0666 tCO2e, or 30.3% of the 0.22 inventory_as_reported upstream factor. ROUTE 2, absolute: 144.5 / 1.7 = 85.0 kt CH4 official basis = 2.53 MtCO2e at 29.8; the 0.22 factor over 63 bcm (45.7 Mt LNG-equivalent at 1.38 bcm per mtpa) implies 10.04 MtCO2e of upstream emissions net of transmission, so the share is 25.2%. BRACKET: across the 1.5-2.0 correction range and AR5 (25) versus AR6 (29.8) methane GWP vintages, the two routes span roughly 18% to 34% and centre near 25%. The derivation therefore CORROBORATES 0.30 as being within range while suggesting it sits high. It does not pin the value, so 0.30 is retained and stays typed assumption.</t>
+          <t>Share of upstream oil and gas emissions that is methane rather than carbon dioxide. Required to apply the measurement correction and the GWP20 uplift to the methane portion only. DERIVED, 3 September 2026, from Johnson, Conrad &amp; Tyner (2023), Communications Earth &amp; Environment, https://doi.org/10.1038/s43247-023-00769-7 , which reports for British Columbia in 2021: total measurement-based upstream oil and gas methane of 144.5 kt/y; an upstream methane intensity of marketed natural gas of 0.38% (95% CI 0.33-0.44%, SI section S3); and that this measurement-based inventory is nominally 1.7 times the official ECCC bottom-up figure (range 1.5-2.0). ROUTE A, intensity: 0.38% / 1.7 = 0.224% official-basis intensity; per tonne of marketed gas that is 0.00224 t CH4, which at GWP100 29.8 is 0.0666 tCO2e, or 30.3% of the 0.22 inventory_as_reported upstream factor. ROUTE B, absolute: 144.5 / 1.7 = 85.0 kt CH4 official basis = 2.53 MtCO2e at 29.8; the 0.22 factor over 63 bcm (45.7 Mt LNG-equivalent at 1.38 bcm per mtpa) implies 10.04 MtCO2e of upstream emissions net of transmission, so the share is 25.2%. BRACKET: across the 1.5-2.0 correction range and AR5 (25) versus AR6 (29.8) methane GWP vintages the two routes span roughly 18% to 34% and centre near 25%. 0.25 is adopted as the centre of that bracket, replacing an assumed 0.30 which sat high in it without a stated reason. Still a judgement within a bracket rather than a single reported figure, so the type stays assumption.</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -2977,7 +2989,7 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>DO NOT substitute the national fugitives share. ECCC's 2026 executive summary reports 46 MtCO2e of oil and gas fugitive methane within roughly 66 MtCO2e of total Fugitive Sources, a share near 70%. This model's upstream stage covers production and processing in total, INCLUDING stationary combustion and flaring, which are nearly all CO2. Applying a fugitives-only share here would overstate methane by roughly a factor of two. Canada's NIR gives about 20% for the oil and gas sector nationally, but that includes oil sands, which are far more CO2-intensive than gas production. SENSITIVITY OF THE MODEL TO THIS VALUE: the central upstream factor is insensitive - 0.22 x (1 - s + 1.5s) gives 0.2530 at s=0.30 and 0.2475 at s=0.25, both rounding to 0.25 - and measurement_high likewise rounds to 0.26 either way. What moves is the near_term_methane_gwp20 scenario (0.428 at s=0.30 against 0.393 at s=0.25) and the CO2/CH4 split in the physics, which flows into the SC-CH4 damages line. OTHER ROUTES ATTEMPTED 3 September 2026 and not closed: the ECCC National Inventory Report Part 3 provincial tables (category 1.B.2 for British Columbia) exist but are served through a JavaScript data-mart portal rather than a direct download, so the CO2/CH4 cells could not be pulled; the UNFCCC Common Reporting Tables for Canada are the route that would work. The BC Provincial Inventory methodology report confirms upstream fugitives are Tier 3 bottom-up facility by facility, so the underlying data distinguishes gases even though the published provincial tables are CO2e only.</t>
+          <t>DO NOT substitute the national fugitives share. ECCC's 2026 executive summary reports 46 MtCO2e of oil and gas fugitive methane within roughly 66 MtCO2e of total Fugitive Sources, a share near 70%. This model's upstream stage covers production and processing in total, INCLUDING stationary combustion and flaring, which are nearly all CO2. Applying a fugitives-only share here would overstate methane by roughly a factor of two. Canada's NIR gives about 20% for the oil and gas sector nationally, but that includes oil sands, which are far more CO2-intensive than gas production. WHAT THIS VALUE DRIVES: the CO2 floor in the per-gas split (inventory_as_reported x (1 - share) = 0.165 at 0.25, was 0.154 at 0.30), and through it lifetime_co2_only_mt, lifetime_ch4_kt and the SC-CH4 damages line; and the near_term_methane_gwp20 scenario factor. It does NOT drive the measurement_central 0.25 or measurement_high 0.26 upstream factors, which are stored values on the Scenarios sheet: 0.22 x (1 - s + 1.5s) is 0.2530 at s=0.30 and 0.2475 at s=0.25, both rounding to the stored 0.25. The headline lifetime, peak and territorial split are therefore unchanged by this move. OTHER ROUTES ATTEMPTED 3 September 2026 and not closed: the ECCC National Inventory Report Part 3 provincial tables (category 1.B.2 for British Columbia) exist but are served through a JavaScript data-mart portal rather than a direct download; the UNFCCC Common Reporting Tables for Canada are the route that would work. The BC Provincial Inventory methodology report confirms upstream fugitives are Tier 3 bottom-up facility by facility, so the underlying data distinguishes gases even though the published provincial tables are CO2e only.</t>
         </is>
       </c>
     </row>
@@ -4679,7 +4691,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>upstream 0.428</t>
+          <t>upstream 0.393</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4694,12 +4706,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Non-methane portion of inventory_as_reported (0.22 x 0.70 = 0.154) is unchanged. Methane portion is inventory x upstream_ch4_share x upstream_measurement_correction x (gwp20_ch4 / gwp100_ch4). Depends on the assumed methane share of 0.30. Was 0.33 (= 0.22 x 1.5 on the whole factor); that treated all upstream as methane.</t>
+          <t>Non-methane portion of inventory_as_reported (0.22 x 0.75 = 0.165) is unchanged. Methane portion is inventory x upstream_ch4_share x upstream_measurement_correction x (gwp20_ch4 / gwp100_ch4). Depends on the methane share of 0.25. Was 0.428 at a share of 0.30, and 0.33 before that (= 0.22 x 1.5 on the whole factor, which treated all upstream as methane).</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Result 0.428 depends on upstream_ch4_share = 0.30. Pipeline methane is not re-weighted: no pipeline methane share exists.</t>
+          <t>Result 0.393 depends on upstream_ch4_share = 0.25, itself the centre of the 18-34% Johnson et al. bracket. Pipeline methane is not re-weighted: no pipeline methane share exists.</t>
         </is>
       </c>
     </row>

--- a/Inputs/Canada_LNG_Data_Inputs.xlsx
+++ b/Inputs/Canada_LNG_Data_Inputs.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1044,6 +1044,25 @@
       <c r="B64" s="4" t="inlineStr">
         <is>
           <t>The Supporting Infrastructure headroom check in the asset register uses lng_to_gas_bcm_per_mtpa from this file. Track membership in the asset register follows the rules defined in the Scenarios tab here. The lifespan sensitivity here references authorised_export_term_years from the asset register.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PARAMETER STATUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>live or reference-only</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Whether the model reads this row. `live` means at least one module in src/ or build_results.py looks the parameter up by name. `reference-only` means no module reads it: the row is documentation, context or the working behind a value that lives elsewhere. Every reference-only row carries a note saying what it is for and, where one exists, naming its live counterpart, so the workbook never holds two disconnected versions of one fact. Added 3 September 2026; the column is derived by tools/mark_reference_only_params.py by scanning the code, not typed by hand.</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1467,6 +1486,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1507,6 +1531,11 @@
           <t>Figure also in the report PDF https://www.datocms-assets.com/146580/1783403747-igu-world-lng-report-2026.pdf (liquefaction capacity chapter). Nameplate utilisation, not available-capacity.</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1538,6 +1567,11 @@
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1569,6 +1603,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1600,6 +1639,11 @@
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1640,6 +1684,11 @@
           <t>Fallback only. Licensed assets use authorised_export_end_year, sourced to the licence filing on Asset Sources (GL-330, GL-340, GL-346, GL-349), not this index page.</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1675,6 +1724,11 @@
           <t>About 25 per cent below the 40 year case</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1711,6 +1765,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1751,6 +1810,11 @@
           <t>URL points at a government summary; the Act itself is the primary source</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1786,6 +1850,11 @@
           <t>Was 3 (assumed). Raised 3 September 2026.</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1821,6 +1890,11 @@
           <t>Unchanged at 5, so the central case is untouched by the 3 September 2026 band change. Applied to the seven proposed assets without FID. post_fid_to_completion = 4.5 rests on the same IEA statement and is reference-only; this row is the one the model reads.</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1856,6 +1930,11 @@
           <t>Was 7 (assumed, symmetric). Raised 3 September 2026.</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1896,6 +1975,11 @@
           <t>Marked reference-only 3 September 2026 so the workbook does not carry two disconnected versions of one fact. Do not wire this into the utilisation calculation without retiring fid_delay_mid.</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>reference-only</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1926,7 +2010,16 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>REFERENCE-ONLY. Read by no module. An earlier three-point band for the multiplier by which measurement-based upstream methane exceeds the reported inventory. LIVE COUNTERPART: upstream_measurement_correction = 1.5 (cited), which is the single multiplier the model applies, and the Scenarios sheet, which carries the actual upstream range as whole factors (0.22 inventory_as_reported, 0.25 measurement_central, 0.26 measurement_high, 0.55 howarth_high). Do not cite this band and upstream_measurement_correction as two independent facts; they are two versions of one.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>reference-only</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1957,7 +2050,16 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>REFERENCE-ONLY. Read by no module. See methane_leakage_low. LIVE COUNTERPART: upstream_measurement_correction = 1.5. This 1.25 is the superseded central; the model uses 1.5.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>reference-only</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1988,7 +2090,16 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>REFERENCE-ONLY. Read by no module. See methane_leakage_low. LIVE COUNTERPART: upstream_measurement_correction = 1.5, and the howarth_high scenario for the genuine upper bracket.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>reference-only</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2025,6 +2136,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2061,6 +2177,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2092,6 +2213,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2127,6 +2253,11 @@
           <t>Read by no module; it backs the stored feedgas_demand_bcm_y and headroom_bcm_y columns on the register's Supporting Infrastructure sheet. Basis recorded 3 September 2026; previously an uncited method constant.</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>reference-only</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2162,7 +2293,16 @@
           <t>2025 Progress Report</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>REFERENCE-ONLY. Read by no module. The reference year against which Canada's 2030 and 2035 targets are expressed, so it is what makes the target numbers interpretable. LIVE COUNTERPARTS: canada_2030_target_high and canada_2035_target_high, read by src/trajectories.py for the target pathway in figures 4, 5 and 6.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>reference-only</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2203,6 +2343,11 @@
           <t>Projected 2026 emissions are 636 Mt, so already missed</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2243,6 +2388,11 @@
           <t>The target is a range, not a point</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2279,6 +2429,11 @@
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2316,7 +2471,12 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>Government's own progress report confirms Canada is not on track</t>
+          <t>REFERENCE-ONLY. Read by no module. The government's own projection of where 2030 emissions actually land, against a target of 417-455. Kept because it is the evidence for the statement that Canada is not on track. LIVE COUNTERPART: canada_2030_overshoot_gap = 200, which is the figure the model reads for the overshoot line.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>reference-only</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2514,16 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>REFERENCE-ONLY. Read by no module. The low end of the 2035 target range. LIVE COUNTERPART: canada_2035_target_high = 417, read by src/trajectories.py:644 for the target pathway. The high end is plotted because it is the less demanding test of the LNG buildout.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>reference-only</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2391,6 +2560,11 @@
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2427,6 +2601,11 @@
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2467,6 +2646,11 @@
           <t>Budget is CO2. Register emissions are GWP100 CO2e. The comparison is CO2e against a CO2 budget and is an approximation; a true CO2-only total is not derivable from this model.</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2507,6 +2691,11 @@
           <t>Budget is CO2. Register emissions are GWP100 CO2e. The comparison is CO2e against a CO2 budget and is an approximation; a true CO2-only total is not derivable from this model.</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2547,6 +2736,11 @@
           <t>Budget is CO2. Register emissions are GWP100 CO2e. The comparison is CO2e against a CO2 budget and is an approximation; a true CO2-only total is not derivable from this model.</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2577,7 +2771,16 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="H32" s="4" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>REFERENCE-ONLY, AND GENUINELY ORPHANED. Read by no module, and it has NO live counterpart: the coal-plant equivalence comparator these three rows would support is in no figure, no slide table and no output. Kept only so the three rows are not silently dropped. See also coal_plant_capacity_factor and coal_tco2e_per_mwh. If a reviewer asks what these are for, the honest answer is: nothing, at present.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>reference-only</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2608,7 +2811,16 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>REFERENCE-ONLY, AND GENUINELY ORPHANED. See coal_plant_reference_mw. No live counterpart; supports no comparator now in the model.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>reference-only</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2639,7 +2851,16 @@
           <t>Not available</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>REFERENCE-ONLY, AND GENUINELY ORPHANED. See coal_plant_reference_mw. No live counterpart; supports no comparator now in the model.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>reference-only</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2680,6 +2901,11 @@
           <t>OBSERVED DATA AS AT JUNE 2026, recorded 3 September 2026 so this assumption is testable rather than merely asserted. The model still uses the assumed ramp; nothing below has been fed back into it. First cargo 30 June 2025 from Train 1; Train 2 entered production November 2025 (GEM, LNG Canada Terminal page, last edited 18 August 2026, https://www.gem.wiki/LNG_Canada_Terminal ; Norton Rose Fulbright, Canadian LNG industry: 2026 outlook). Vessel departures 4 in December 2025, 10 in January 2026 and 11 in February 2026 (Kpler, via Globe and Mail, 18 March 2026, https://www.theglobeandmail.com/business/article-lng-canada-exports-asia-natural-gas-strait-of-hormuz/ ). Approximately 4.6 Mt exported between June 2025 and mid-March 2026 (RBC Capital Markets, Michael Harvey, same article). 60th cargo mid-March 2026 and approximately 80 cargoes by early May 2026 (EnergyNow, June 2026). April 2026 was the first month above 1 Mt, and production reached 1.2 Mt per month by May 2026. WHAT THE DATA SAYS ABOUT THE ASSUMPTION: against 14 mtpa nameplate, calendar 2025 ran at roughly 11 per cent of a full year against the assumed year-one 25 per cent, while April and May 2026 ran at about 86 and 103 per cent of nameplate against the assumed year-two 60 per cent. THE AVERAGE IS ABOUT RIGHT; THE SHAPE IS NOT. The model starts too high and ramps too slowly, and the two errors largely offset over the life. Retained as a known limitation rather than corrected, because a single-facility observed profile is not a basis for the generic ramp applied to every other asset.</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2720,6 +2946,11 @@
           <t>OBSERVED DATA AS AT JUNE 2026, recorded 3 September 2026 so this assumption is testable rather than merely asserted. The model still uses the assumed ramp; nothing below has been fed back into it. First cargo 30 June 2025 from Train 1; Train 2 entered production November 2025 (GEM, LNG Canada Terminal page, last edited 18 August 2026, https://www.gem.wiki/LNG_Canada_Terminal ; Norton Rose Fulbright, Canadian LNG industry: 2026 outlook). Vessel departures 4 in December 2025, 10 in January 2026 and 11 in February 2026 (Kpler, via Globe and Mail, 18 March 2026, https://www.theglobeandmail.com/business/article-lng-canada-exports-asia-natural-gas-strait-of-hormuz/ ). Approximately 4.6 Mt exported between June 2025 and mid-March 2026 (RBC Capital Markets, Michael Harvey, same article). 60th cargo mid-March 2026 and approximately 80 cargoes by early May 2026 (EnergyNow, June 2026). April 2026 was the first month above 1 Mt, and production reached 1.2 Mt per month by May 2026. WHAT THE DATA SAYS ABOUT THE ASSUMPTION: against 14 mtpa nameplate, calendar 2025 ran at roughly 11 per cent of a full year against the assumed year-one 25 per cent, while April and May 2026 ran at about 86 and 103 per cent of nameplate against the assumed year-two 60 per cent. THE AVERAGE IS ABOUT RIGHT; THE SHAPE IS NOT. The model starts too high and ramps too slowly, and the two errors largely offset over the life. Retained as a known limitation rather than corrected, because a single-facility observed profile is not a basis for the generic ramp applied to every other asset.</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2760,6 +2991,11 @@
           <t>OBSERVED DATA AS AT JUNE 2026, recorded 3 September 2026 so this assumption is testable rather than merely asserted. The model still uses the assumed ramp; nothing below has been fed back into it. First cargo 30 June 2025 from Train 1; Train 2 entered production November 2025 (GEM, LNG Canada Terminal page, last edited 18 August 2026, https://www.gem.wiki/LNG_Canada_Terminal ; Norton Rose Fulbright, Canadian LNG industry: 2026 outlook). Vessel departures 4 in December 2025, 10 in January 2026 and 11 in February 2026 (Kpler, via Globe and Mail, 18 March 2026, https://www.theglobeandmail.com/business/article-lng-canada-exports-asia-natural-gas-strait-of-hormuz/ ). Approximately 4.6 Mt exported between June 2025 and mid-March 2026 (RBC Capital Markets, Michael Harvey, same article). 60th cargo mid-March 2026 and approximately 80 cargoes by early May 2026 (EnergyNow, June 2026). April 2026 was the first month above 1 Mt, and production reached 1.2 Mt per month by May 2026. WHAT THE DATA SAYS ABOUT THE ASSUMPTION: against 14 mtpa nameplate, calendar 2025 ran at roughly 11 per cent of a full year against the assumed year-one 25 per cent, while April and May 2026 ran at about 86 and 103 per cent of nameplate against the assumed year-two 60 per cent. THE AVERAGE IS ABOUT RIGHT; THE SHAPE IS NOT. The model starts too high and ramps too slowly, and the two errors largely offset over the life. Retained as a known limitation rather than corrected, because a single-facility observed profile is not a basis for the generic ramp applied to every other asset.</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2797,6 +3033,11 @@
           <t>Fallback only for domestic plants that still carry not_published. Export and bunkering assets are recorded as gas_turbine. Electric drive is not assumed for any terminal.</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2837,6 +3078,11 @@
           <t>Applying nameplate utilisation here overstates the terminal's emissions roughly thirtyfold</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2872,6 +3118,11 @@
           <t>Used to convert Saint John's reported throughput in TBtu into tonnes. Recorded 3 September 2026; previously an uncited method constant.</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2912,6 +3163,11 @@
           <t>Gives the 50 year lifespan sensitivity a legal basis</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2952,6 +3208,11 @@
           <t>Typed assumption. The interval is 191 to 229 Mt.</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2992,6 +3253,11 @@
           <t>DO NOT substitute the national fugitives share. ECCC's 2026 executive summary reports 46 MtCO2e of oil and gas fugitive methane within roughly 66 MtCO2e of total Fugitive Sources, a share near 70%. This model's upstream stage covers production and processing in total, INCLUDING stationary combustion and flaring, which are nearly all CO2. Applying a fugitives-only share here would overstate methane by roughly a factor of two. Canada's NIR gives about 20% for the oil and gas sector nationally, but that includes oil sands, which are far more CO2-intensive than gas production. WHAT THIS VALUE DRIVES: the CO2 floor in the per-gas split (inventory_as_reported x (1 - share) = 0.165 at 0.25, was 0.154 at 0.30), and through it lifetime_co2_only_mt, lifetime_ch4_kt and the SC-CH4 damages line; and the near_term_methane_gwp20 scenario factor. It does NOT drive the measurement_central 0.25 or measurement_high 0.26 upstream factors, which are stored values on the Scenarios sheet: 0.22 x (1 - s + 1.5s) is 0.2530 at s=0.30 and 0.2475 at s=0.25, both rounding to the stored 0.25. The headline lifetime, peak and territorial split are therefore unchanged by this move. OTHER ROUTES ATTEMPTED 3 September 2026 and not closed: the ECCC National Inventory Report Part 3 provincial tables (category 1.B.2 for British Columbia) exist but are served through a JavaScript data-mart portal rather than a direct download; the UNFCCC Common Reporting Tables for Canada are the route that would work. The BC Provincial Inventory methodology report confirms upstream fugitives are Tier 3 bottom-up facility by facility, so the underlying data distinguishes gases even though the published provincial tables are CO2e only.</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3032,6 +3298,11 @@
           <t>Applied to the methane portion only</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3072,6 +3343,11 @@
           <t>Equals Emission Factors liquefaction central. Applied to every terminal for its whole operating life as of August 2026.</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3107,6 +3383,11 @@
           <t>Figure-8 appendix counterfactual and Emission Factors range_low. NOT used in the central case, which is gas turbine 0.29 for every terminal. BC EAO 0.021 grid / 0.156 gas-barge are a separate SI sensitivity on a facility-total boundary.</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3144,7 +3425,12 @@
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>A gas turbine facility at 0.29 exceeds this by 0.13, about 1.8 Mt/yr across 14 mtpa</t>
+          <t>REFERENCE-ONLY. Read by no module. The British Columbia LNG emission intensity benchmark, kept as the yardstick a reviewer will hold the liquefaction factor against. LIVE COUNTERPARTS: the Emission Factors liquefaction central of 0.29 tCO2e/t LNG, which exceeds this benchmark by 0.13 (about 1.8 Mt/yr across 14 mtpa), and the electric-drive sensitivity in src/drive_sensitivity.py, which is the case in which a facility could approach it.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>reference-only</t>
         </is>
       </c>
     </row>
@@ -3187,6 +3473,11 @@
           <t>One way</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3219,7 +3510,12 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>One way</t>
+          <t>REFERENCE-ONLY. Read by no module. The comparator voyage a reviewer reaches for when asking whether a British Columbia route is short. LIVE COUNTERPART: route_bc_to_northeast_asia_nm = 3800, and the route_distance_nm column on the Asset Register, which is what src/model.route_scale_factor actually reads to scale shipping per asset.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>reference-only</t>
         </is>
       </c>
     </row>
@@ -3257,7 +3553,16 @@
           <t>2025</t>
         </is>
       </c>
-      <c r="H50" s="4" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>REFERENCE-ONLY. Read by no module. Voyage duration for the British Columbia to north-east Asia run, kept as context for the shipping factor. LIVE COUNTERPART: route_bc_to_northeast_asia_nm = 3800 and the Emission Factors shipping central of 0.12; the model works in distance, not days.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>reference-only</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3293,7 +3598,16 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="H51" s="4" t="inlineStr"/>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>REFERENCE-ONLY as a Parameters row: read by no module HERE. It is not dead data. LIVE COUNTERPART: it is the same number as the Emission Factors shipping range_low of 0.05 tCO2e/t, which the Monte Carlo does sample. This row is the duplicate; the Emission Factors cell is the one that runs. Change that cell, not this one.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>reference-only</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3329,7 +3643,16 @@
           <t>2021</t>
         </is>
       </c>
-      <c r="H52" s="4" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>REFERENCE-ONLY as a Parameters row: read by no module HERE. LIVE COUNTERPART: the same number as the Emission Factors shipping range_high of 0.31 tCO2e/t, which the Monte Carlo samples. This row is the duplicate; the Emission Factors cell is the one that runs.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>reference-only</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3367,7 +3690,12 @@
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Not applied to Pacific routes</t>
+          <t>REFERENCE-ONLY. Read by no module. The great-circle-to-sailing-distance uplift used when the Atlantic route distances below were derived, calibrated on route_saint_john_to_rotterdam_nm. LIVE COUNTERPART: the route_distance_nm column on the Asset Register, which holds the finished distances this factor was used to produce; that column is what src/model.route_scale_factor reads. This row is the working, not the result.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>reference-only</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3735,12 @@
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>Estimate, not a published sailing distance</t>
+          <t>REFERENCE-ONLY. Read by no module. Derived with route_atlantic_routing_factor; an estimate, not a published sailing distance. LIVE COUNTERPART: this asset's route_distance_nm cell on the Asset Register, which is the value the model reads.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>reference-only</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3780,12 @@
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>Estimate, not a published sailing distance</t>
+          <t>REFERENCE-ONLY. Read by no module. Derived with route_atlantic_routing_factor; an estimate, not a published sailing distance. LIVE COUNTERPART: this asset's route_distance_nm cell on the Asset Register.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>reference-only</t>
         </is>
       </c>
     </row>
@@ -3487,7 +3825,12 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>The calibration point for the Atlantic routing factor</t>
+          <t>REFERENCE-ONLY. Read by no module. The one cited Atlantic sailing distance, and the calibration point from which route_atlantic_routing_factor was derived. LIVE COUNTERPART: this asset's route_distance_nm cell on the Asset Register.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>reference-only</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3870,12 @@
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>Use to scale shipping by route distance</t>
+          <t>REFERENCE-ONLY. Read by no module. The IMO Data Collection System fleet figure behind the independent reconstruction of the shipping factor: 8.50 gCO2/DWT/nm over a 7,600 nm round trip, converted to cargo tonnes with cargo_tonnes_per_dwt and uplifted 44 per cent for measured methane slip, giving 0.110. LIVE COUNTERPART: the Emission Factors shipping central of 0.12 tCO2e/t, which this reconstruction independently supports and which its range_sources cell describes in full.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>reference-only</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3915,12 @@
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>Per ship, not per tonne of cargo</t>
+          <t>REFERENCE-ONLY. Read by no module. Per ship, not per tonne of cargo, so it cannot be used as an intensity without a cargo denominator. Kept as the absolute-terms cross-check on lng_carrier_aer_gco2_per_dwt_nm. LIVE COUNTERPART: the Emission Factors shipping central of 0.12 tCO2e/t.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>reference-only</t>
         </is>
       </c>
     </row>
@@ -3610,6 +3963,11 @@
           <t>Applies to the shipping stage only</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3642,7 +4000,12 @@
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>Sensitivity worth testing</t>
+          <t>REFERENCE-ONLY. Read by no module. The cargo-to-deadweight ratio that converts lng_carrier_aer_gco2_per_dwt_nm into an intensity per tonne of LNG in the README shipping reconstruction. Still uncited, and listed in Outputs/CITATIONS_WANTED.md as such. LIVE COUNTERPART: the Emission Factors shipping central of 0.12 tCO2e/t. Because no module reads this row, the open citation affects the reconstruction narrative only, not any published number.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>reference-only</t>
         </is>
       </c>
     </row>
@@ -3687,6 +4050,11 @@
           <t>Electric drive is not assumed for any terminal. Of the projects claiming electrification, only Cedar and Woodfibre have interconnection works under construction; the remainder rest on memoranda of understanding, aspirations conditional on transmission that has not been built, or statements with no firm date. Ksi Lisims holds an MOU with BC Hydro for up to 600 MW conditional on the North Coast Transmission Line expansion, which is not built. LNG Canada Phase 2 states an intention to transition to electric motors as more renewable power becomes available, with no date and no contracted supply. There is not sufficient evidence that electric drive will be in use at these facilities, and a commitment contingent on infrastructure that does not exist is not a basis for lowering the emissions factor. Where electrification is later contracted and built, this assumption should be revisited.</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3725,6 +4093,11 @@
           <t>Central value 2030. Sensitivity at 2033 and 2035 is reported. Summit Lake states a 30-year life; the other five use lifecycle_years_default.</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3763,6 +4136,11 @@
           <t>Do not reuse a draw sequence across published runs without recording a new seed.</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3801,6 +4179,11 @@
           <t>10,000 draws for stable 5th/95th percentiles.</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3841,6 +4224,11 @@
           <t>Headline results include assets whose chain is in headline_scope_chains and whose calc_group is in headline_scope_calc_groups. Domestic peak-shaving and other non-export assets are out of headline; they stay in the register. Inventing a 1971/1976 retirement date is not supported.</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3881,6 +4269,11 @@
           <t>Headline results include assets whose chain is in headline_scope_chains and whose calc_group is in headline_scope_calc_groups. Domestic peak-shaving and other non-export assets are out of headline; they stay in the register. Inventing a 1971/1976 retirement date is not supported.</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3921,6 +4314,11 @@
           <t>SENSITIVITY ONLY - the central liquefaction factor stays 0.29 for every terminal. BOUNDARY: this is the facility total intensity including marine sources, not the liquefaction stage alone, so it is not like for like with the 0.29 liquefaction factor on the Emission Factors sheet. Any comparison against 0.29 is therefore approximate and is labelled as such wherever it is reported.</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3961,6 +4359,11 @@
           <t>SENSITIVITY ONLY - the central liquefaction factor stays 0.29 for every terminal. BOUNDARY: this is the facility total intensity including marine sources, not the liquefaction stage alone, so it is not like for like with the 0.29 liquefaction factor on the Emission Factors sheet. Any comparison against 0.29 is therefore approximate and is labelled as such wherever it is reported.</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4001,6 +4404,11 @@
           <t>Figure 10 only. Not mixed with this model's GWP100 totals.</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4041,6 +4449,11 @@
           <t>Figure 10 only.</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4081,6 +4494,11 @@
           <t>Figure 10 only.</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4121,6 +4539,11 @@
           <t>Figure 10 only.</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4161,6 +4584,11 @@
           <t>Figure 10 only.</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4201,6 +4629,11 @@
           <t>Figure 10. Converted with lca_hhv_mj_per_kg.</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4241,6 +4674,11 @@
           <t>Figure 10.</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4281,6 +4719,11 @@
           <t>Figure 10 conversion only.</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>live</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4321,6 +4764,11 @@
       <c r="H77" t="inlineStr">
         <is>
           <t>SI only. Do not treat as filed first-export years.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
     </row>

--- a/Inputs/Canada_LNG_Data_Inputs.xlsx
+++ b/Inputs/Canada_LNG_Data_Inputs.xlsx
@@ -1706,22 +1706,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>assumption</t>
+          <t>cited</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>Lower bound for the lifespan sensitivity. Matches the operating life Summit Lake PG LNG states in its impact assessment.</t>
+          <t>Lower bound for the lifespan sensitivity, and now a cited one. JX LNG Canada Ltd., Summit Lake PG LNG Project - Liquified Natural Gas Facility, INITIAL PROJECT DESCRIPTION (BCEAA 2018, IAA 2019), prepared by Keywest Projects Ltd., 12 February 2024. PAGE 11 OF 106, under the heading 'Estimates and Purpose': 'The Project is expected to operate for 30 years.' Stated again on page 52, section 5 Decommissioning: 'The decommissioning process for the Project is set to commence after a minimum of 30 years after the anticipated phase 1 construction year.' The same sentence appears on page 6 of 17 of the English Summary filed with the Impact Assessment Agency of Canada, https://ceaa.gc.ca/050/documents/p87307/155565E.pdf . NOTE ON THE FILENAME: the British Columbia Environmental Assessment Office registry stores the file as 'Draft Initial Project Description.pdf' while the document's own title page reads 'Initial Project Description'; the link is to that document, not a different one. Registry landing page: https://projects.eao.gov.bc.ca/p/65c661a8399db00022d48849/documents ; federal registry: https://iaac-aeic.gc.ca/050/evaluations/proj/87307?culture=en-CA . NOTE ON STATUS: the Agency suspended the impact assessment timeline on 19 July 2024 at the proponent's request, so the assessment is paused rather than complete. The 30 years is the proponent's own stated design life and does not depend on the assessment concluding. Located and opened 3 September 2026; source_url was 'Not available' until then.</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Not available</t>
-        </is>
+          <t>https://www.projects.eao.gov.bc.ca/api/public/document/65cce8f768c392001b2d5692/download/Draft%20Initial%20Project%20Description.pdf</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>2024</v>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>About 25 per cent below the 40 year case</t>
+          <t>About 25 per cent below the 40 year case. The 30 years is one proponent's stated design life, not an industry norm: the four main export projects in this register run on 40 year CER export licence terms (lifecycle_years_default), and the CER may issue licences of up to 50 years (lifespan_sensitivity_high). The three together bracket the life assumption from a real short case to a real regulatory ceiling.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">

--- a/Inputs/Canada_LNG_Data_Inputs.xlsx
+++ b/Inputs/Canada_LNG_Data_Inputs.xlsx
@@ -798,7 +798,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>CER reports British Columbia oil and gas production, processing and transmission emissions of 14.6 MtCO2e for 2022, against roughly 63 bcm/y of marketable gas. Net of pipeline transport this gives 0.22 tCO2e per tonne of LNG. Peer-reviewed measurement studies find Canadian inventories understate upstream methane by 1.5 to 1.7 times, placing the central value near 0.30.</t>
+          <t>CER reports British Columbia oil and gas production, processing and transmission emissions of 14.6 MtCO2e for 2022, against roughly 63 bcm/y of marketable gas: 0.320 tCO2e per tonne of LNG including transmission. Net of the model's own pipeline_transport central (0.074) this gives 0.246. Peer-reviewed measurement studies find Canadian inventories understate upstream methane by 1.5 to 1.7 times; applied to a 0.25 methane share that gives a central of 0.277. Every step is in the Emission Factors basis cell. Re-derived 3 September 2026; the earlier 0.22 had netted the retired pipeline 0.10.</t>
         </is>
       </c>
     </row>
@@ -1166,17 +1166,17 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.25</v>
+        <v>0.277</v>
       </c>
       <c r="F2" t="n">
-        <v>0.22</v>
+        <v>0.246</v>
       </c>
       <c r="G2" t="n">
         <v>0.55</v>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>Derived from Canadian data: CER reports BC oil and gas production, processing and transmission emissions of 14.6 MtCO2e (2022) against roughly 63 bcm/y of marketable gas. Net of pipeline transport that gives 0.22 tCO2e/t LNG on the official inventory. Peer-reviewed measurement studies find Canadian inventories understate upstream methane by 1.5 to 1.7 times, Applied to the methane portion only, at an assumed 30 per cent methane share, that gives a central value of 0.25. https://www.cer-rec.gc.ca/en/data-analysis/energy-markets/provincial-territorial-energy-profiles/provincial-territorial-energy-profiles-british-columbia.html</t>
+          <t>DERIVED, every step shown; re-derived 3 September 2026 on the current pipeline factor. (1) ANCHOR: the Canada Energy Regulator reports British Columbia oil and gas production, processing AND transmission emissions of 14.6 MtCO2e for 2022 against roughly 63 bcm/y of marketable gas (https://www.cer-rec.gc.ca/en/data-analysis/energy-markets/provincial-territorial-energy-profiles/provincial-territorial-energy-profiles-british-columbia.html). (2) CONVERSION: 63 bcm / 1.38 bcm per Mt LNG (lng_to_gas_bcm_per_mtpa) = 45.65 Mt LNG-equivalent, so the anchor is 14.6 / 45.65 = 0.3198 tCO2e per t LNG INCLUDING transmission. (3) NET OF PIPELINE: transmission is this model's separate pipeline_transport stage, so its current central of 0.074 is removed: 0.3198 - 0.074 = 0.2458, stored as 0.246. This is the official inventory upstream factor and the inventory_as_reported scenario. (4) METHANE SHARE: upstream_ch4_share = 0.25, the centre of the Johnson et al. (2023) bracket. (5) CORRECTION: peer-reviewed measurement studies find Canadian inventories understate upstream methane by 1.5 to 1.7 times; upstream_measurement_correction = 1.5 is applied to the methane portion only. (6) RESULT: 0.246 x (1 - 0.25 + 1.5 x 0.25) = 0.246 x 1.125 = 0.2765, stored as 0.277. HISTORY: until 3 September 2026 the cell read 'net of pipeline transport that gives 0.22', which had netted the RETIRED pipeline value of 0.10 (0.320 - 0.10 = 0.220); when pipeline moved to 0.074 that arithmetic stopped closing and the chain dropped about -0.026 t/t against its own anchor. Central was 0.25 (0.2475 at two decimals). Values are now stored to three decimals because at two the stored central did not visibly depend on the methane share; at three it does: 0.246 x (1 + 0.5 x 0.30) = 0.283 at a share of 0.30. The measurement_high (1.7x) and near_term_methane_gwp20 scenarios are rescaled from the same 0.246 base on the Scenarios sheet.</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>The largest uncertainty in the model. BC does not publish the CO2 and methane split for upstream emissions, so the 30 per cent methane share is an assumption tested across 20 to 40 per cent. The national oil and gas figure is 20 per cent methane, but that includes oil sands, which are far more carbon dioxide intensive than gas production. Measurement studies also find Montney intensity is among the lowest in North America, while BC reports a 51 per cent methane reduction by 2023, both of which argue against the high case.</t>
+          <t>The largest uncertainty in the model. BC does not publish the CO2 and methane split for upstream emissions, so the methane share is a bracketed judgement (upstream_ch4_share = 0.25, from Johnson et al. 2023; tested across 0.20 to 0.40). The national oil and gas figure is 20 per cent methane, but that includes oil sands, which are far more carbon dioxide intensive than gas production. Measurement studies also find Montney intensity is among the lowest in North America, while BC reports a 51 per cent methane reduction by 2023, both of which argue against the high case.</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>0.074 tCO2e per t LNG, from two independent routes that converge. ROUTE A (central): Liu, R.E., Ravikumar, A.P., Bi, X.T., Zhang, S., Nie, Y., Brandt, A., Bergerson, J.A. (2021), 'Greenhouse Gas Emissions of Western Canadian Natural Gas: Proposed Emissions Tracking for Life Cycle Modeling', Environmental Science &amp; Technology 55(14): 9711-9720, https://doi.org/10.1021/acs.est.0c06353 (open PDF https://ngi.stanford.edu/sites/ngi/files/media/file/acs.est_.0c06353.pdf). Results, p. 9713: 'The company emissions intensities using both mass and energy allocation are 4.2 gCO2e/MJ NG at transmission pipeline outlet.' Modern West Advisory for Emissions Reduction Alberta (2022), Life-Cycle Analysis of Canadian Natural Gas: A Pilot Study, section 5.3 p. 43, https://www.eralberta.ca/wp-content/uploads/2022/04/Modern-West-Advisory-Final-Outcomes-Report-Non-Confidential.pdf , restates that same study on the plant-exit boundary: 'If the transmission emissions are excluded to make the boundaries consistent with the present report, the estimated emission intensity at NG plant exit is approximately 2.86 gCO2e/MJ NG.' The difference is the transmission stage: 4.20 - 2.86 = 1.34 gCO2e/MJ. At lng_energy_content 52 MMBtu/t = 54.863 GJ/t that is 0.0735 tCO2e per t LNG. ROUTE B (independent cross-check, not the central): CER Market Snapshot, 'Greening Canada's pipeline infrastructure' (2022), https://www.cer-rec.gc.ca/en/data-analysis/energy-markets/market-snapshots/2022/market-snapshot-greening-canadas-pipeline-infrastructure.html : 'In 2019, emissions resulting from pipeline transport, primarily emissions related to combustion at compressor stations, accounted for 8.3 MT CO2e', attributed to ECCC National Inventory Report 1990-2019 Part 1 Table 2-5. Over roughly 170 bcm of Canadian marketable gas at 36 PJ/bcm: 8.3 Mt / 6,120 PJ = 1.356 gCO2e/MJ = 0.0744 tCO2e/t. The two routes agree to within 1.2 per cent. Stored as 0.074. Replaces an assumed 0.10 (3 September 2026), which was about 35 per cent above both routes and which no ICF or Sphera document supported. CAVEATS ON ROUTE A. Liu et al. is a case study of Seven Generations Energy's Kakwa operations in Alberta - one operator running relatively new facilities, so plausibly better than the Western Canadian average; the paper's own comparison puts BC estimates at 6.2-12 gCO2e/MJ upstream against its 4.2. The paper's Table 1 Section D gives the modelled transmission pipeline length as 1,100 km (company data; US default 971 km). NOTE THE ABSTRACT SAYS 3.1-4.0 gCO2e/MJ while the Results text says 4.2 for mass and energy allocation and 3.1 / 3.3 for financial and condensate-displacement allocation; the 4.2 used here is the Results figure on the allocation basis this model uses. DISTANCE. This model applies the pipeline factor FLAT, with no distance scaling, unlike shipping. Route A is calibrated on 1,100 km and Route B is a national average haul, while the in-scope feedgas lines are Coastal GasLink 670 km, Prince Rupert Gas Transmission 750 km and FortisBC Eagle Mountain 47 km. If transmission emissions scale with distance, 0.074 is high for every one of them - Woodfibre most of all. That is a stated limitation, not a correction applied here. The Coastal GasLink check (model 1.47 against 1.48 MtCO2e/yr implied by the 2014 BC EAO assessment) confirms the arithmetic of scaling a factor with throughput; it is not an independent measurement of the factor.</t>
+          <t>0.074 tCO2e per t LNG, from two independent routes that converge. ROUTE A (central): Liu, R.E., Ravikumar, A.P., Bi, X.T., Zhang, S., Nie, Y., Brandt, A., Bergerson, J.A. (2021), 'Greenhouse Gas Emissions of Western Canadian Natural Gas: Proposed Emissions Tracking for Life Cycle Modeling', Environmental Science &amp; Technology 55(14): 9711-9720, https://doi.org/10.1021/acs.est.0c06353 (open PDF https://ngi.stanford.edu/sites/ngi/files/media/file/acs.est_.0c06353.pdf). Results, p. 9713: 'The company emissions intensities using both mass and energy allocation are 4.2 gCO2e/MJ NG at transmission pipeline outlet.' Modern West Advisory for Emissions Reduction Alberta (2022), Life-Cycle Analysis of Canadian Natural Gas: A Pilot Study, section 5.3 p. 43, https://www.eralberta.ca/wp-content/uploads/2022/04/Modern-West-Advisory-Final-Outcomes-Report-Non-Confidential.pdf , restates that same study on the plant-exit boundary: 'If the transmission emissions are excluded to make the boundaries consistent with the present report, the estimated emission intensity at NG plant exit is approximately 2.86 gCO2e/MJ NG.' The difference is the transmission stage: 4.20 - 2.86 = 1.34 gCO2e/MJ. At lng_energy_content 52 MMBtu/t = 54.863 GJ/t that is 0.0735 tCO2e per t LNG. ROUTE B (independent cross-check, not the central): CER Market Snapshot, 'Greening Canada's pipeline infrastructure' (2022), https://www.cer-rec.gc.ca/en/data-analysis/energy-markets/market-snapshots/2022/market-snapshot-greening-canadas-pipeline-infrastructure.html : 'In 2019, emissions resulting from pipeline transport, primarily emissions related to combustion at compressor stations, accounted for 8.3 MT CO2e', attributed to ECCC National Inventory Report 1990-2019 Part 1 Table 2-5. Over roughly 170 bcm of Canadian marketable gas at 36 PJ/bcm: 8.3 Mt / 6,120 PJ = 1.356 gCO2e/MJ = 0.0744 tCO2e/t. The two routes agree to within 1.2 per cent. Stored as 0.074. Replaces an assumed 0.10 (3 September 2026), which was about 35 per cent above both routes and which no ICF or Sphera document supported. CAVEATS ON ROUTE A. Liu et al. is a case study of Seven Generations Energy's Kakwa operations in Alberta - one operator running relatively new facilities, so plausibly better than the Western Canadian average; the paper's own comparison puts BC estimates at 6.2-12 gCO2e/MJ upstream against its 4.2. The paper's Table 1 Section D gives the modelled transmission pipeline length as 1,100 km (company data; US default 971 km). NOTE THE ABSTRACT SAYS 3.1-4.0 gCO2e/MJ while the Results text says 4.2 for mass and energy allocation and 3.1 / 3.3 for financial and condensate-displacement allocation; the 4.2 used here is the Results figure on the allocation basis this model uses. DISTANCE. This model applies the pipeline factor FLAT, with no distance scaling, unlike shipping. Route A is calibrated on 1,100 km and Route B is a national average haul, while the in-scope feedgas lines are Coastal GasLink 670 km, Prince Rupert Gas Transmission 750 km and FortisBC Eagle Mountain 47 km. If transmission emissions scale with distance, 0.074 is high for every one of them - Woodfibre most of all. That is a stated limitation, not a correction applied here. THREE EVIDENCE POINTS, RECONCILED. (i) The 2014 BC Environmental Assessment Office assessment of Coastal GasLink puts operations at 3.517 MtCO2e/yr at the line's full 5 Bcf/d design capacity (51.7 bcm/y, 37.4 Mt LNG-equivalent at 1.38 bcm per Mt), which implies about 0.094 tCO2e per t LNG - a BRITISH COLUMBIA figure for an in-scope line. (ii) The retired 0.10 was an assumption that the CGL figure happened to sit near; the old '1.47 vs 1.48 MtCO2e/yr' check confirmed only the arithmetic of scaling an assumed factor with throughput and is withdrawn. (iii) The adopted 0.074 comes from an Alberta line (Liu et al. 2021) and a national average (CER/ECCC), not from British Columbia. This model's stated principle is that Canadian sources are used wherever the stage occurs in Canada, and here BC-specific evidence exists and was not adopted. The reason: the CGL figure is a PRE-OPERATION PROJECTION from an environmental assessment, whereas Liu et al. is peer-reviewed and measurement-informed and the CER route is an observed national inventory, and the two independent routes agreeing to 1.2 per cent is the stronger evidence. The CGL projection is 27 per cent above the adopted value; if the line operates at its assessed intensity the factor is low for the LNG Canada / Cedar share of throughput by about that margin, worth roughly 1 MtCO2e/yr at 14 mtpa. That is recorded as a limitation rather than corrected, and the 0.037-0.133 sampled band covers it.</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>IPCC default combustion factor for natural gas. Determined by the carbon content of the fuel, so not location specific and not contestable. https://www.ipcc-nggip.iges.or.jp/public/2006gl/</t>
+          <t>2.75 tCO2 per tonne of LNG is the STOICHIOMETRIC value for pure methane (44/16): one tonne of CH4 burned completely yields 2.75 tonnes of CO2. It is the right central for LNG because liquefaction strips inerts (N2, CO2) and most heavier fractions, so delivered LNG is closer to pure methane than pipeline gas. The IPCC 2006 Guidelines default for natural gas is 2.693 tCO2/t (Table 2.2, 56,100 kgCO2/TJ x Table 1.2 NCV 48.0 TJ/Gg), which is a PIPELINE-gas figure carrying a heavier average composition; it is used here only for the uncertainty band in range_sources, applied as a relative interval to the 2.75 central. Determined by the carbon content of the fuel, so not location specific. https://www.ipcc-nggip.iges.or.jp/public/2006gl/ . Cell rewritten 3 September 2026 to match the README; it previously opened 'IPCC default combustion factor for natural gas', which was not what the 2.75 is.</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Volume of natural gas from one Mt of LNG, used for feedgas headroom against pipeline capacity and the Fermeuse capacity derivation. Basis: LNG density about 450 kg/m3 and a liquid-to-gas expansion ratio near 600:1 at 15 degrees C and 101.325 kPa. The Energy Institute Statistical Review conversion gives 1.36 bcm per Mt on its own density and reference conditions; 1.38 is 1.5% higher and is retained. At 1.36 the Fermeuse derivation gives 5.05 mtpa rather than 4.98, so it rounds to 5.0 either way and no published figure moves.</t>
+          <t>Volume of natural gas from one Mt of LNG, used for feedgas headroom against pipeline capacity and the Fermeuse capacity derivation. Basis: LNG density about 450 kg/m3 and a liquid-to-gas expansion ratio near 600:1 at 15 degrees C and 101.325 kPa. The Energy Institute Statistical Review conversion gives 1.36 bcm per Mt on its own density and reference conditions; 1.38 is 1.5% higher and is retained. At 1.36 the Fermeuse derivation gives 4.57 mtpa rather than 4.51 (both net of liquefaction fuel), so it rounds to 4.5 either way and no published figure moves.</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Share of upstream oil and gas emissions that is methane rather than carbon dioxide. Required to apply the measurement correction and the GWP20 uplift to the methane portion only. DERIVED, 3 September 2026, from Johnson, Conrad &amp; Tyner (2023), Communications Earth &amp; Environment, https://doi.org/10.1038/s43247-023-00769-7 , which reports for British Columbia in 2021: total measurement-based upstream oil and gas methane of 144.5 kt/y; an upstream methane intensity of marketed natural gas of 0.38% (95% CI 0.33-0.44%, SI section S3); and that this measurement-based inventory is nominally 1.7 times the official ECCC bottom-up figure (range 1.5-2.0). ROUTE A, intensity: 0.38% / 1.7 = 0.224% official-basis intensity; per tonne of marketed gas that is 0.00224 t CH4, which at GWP100 29.8 is 0.0666 tCO2e, or 30.3% of the 0.22 inventory_as_reported upstream factor. ROUTE B, absolute: 144.5 / 1.7 = 85.0 kt CH4 official basis = 2.53 MtCO2e at 29.8; the 0.22 factor over 63 bcm (45.7 Mt LNG-equivalent at 1.38 bcm per mtpa) implies 10.04 MtCO2e of upstream emissions net of transmission, so the share is 25.2%. BRACKET: across the 1.5-2.0 correction range and AR5 (25) versus AR6 (29.8) methane GWP vintages the two routes span roughly 18% to 34% and centre near 25%. 0.25 is adopted as the centre of that bracket, replacing an assumed 0.30 which sat high in it without a stated reason. Still a judgement within a bracket rather than a single reported figure, so the type stays assumption.</t>
+          <t>Share of upstream oil and gas emissions that is methane rather than carbon dioxide. Required to apply the measurement correction and the GWP20 uplift to the methane portion only. DERIVED, 3 September 2026, from Johnson, Conrad &amp; Tyner (2023), Communications Earth &amp; Environment, https://doi.org/10.1038/s43247-023-00769-7 , which reports for British Columbia in 2021: total measurement-based upstream oil and gas methane of 144.5 kt/y; an upstream methane intensity of marketed natural gas of 0.38% (95% CI 0.33-0.44%, SI section S3); and that this measurement-based inventory is nominally 1.7 times the official ECCC bottom-up figure (range 1.5-2.0). ROUTE A, intensity: 0.38% / 1.7 = 0.224% official-basis intensity; per tonne of marketed gas that is 0.00224 t CH4, which at GWP100 29.8 is 0.0666 tCO2e, or 27.1% of the 0.246 inventory_as_reported upstream factor (30.3% of the pre-3-September 0.22). ROUTE B, absolute: 144.5 / 1.7 = 85.0 kt CH4 official basis = 2.53 MtCO2e at 29.8; the 0.246 factor over 63 bcm (45.7 Mt LNG-equivalent at 1.38 bcm per mtpa) implies 11.22 MtCO2e of upstream emissions net of transmission, so the share is 22.5% (25.2% on the pre-3-September 0.22 base). BRACKET: across the 1.5-2.0 correction range and AR5 (25) versus AR6 (29.8) methane GWP vintages the two routes span roughly 18% to 34% and centre near 25%. On the re-derived 0.246 base (3 September 2026) the two routes give 27.1% and 22.5%, which still straddle 25; the bracket and the adopted value are unchanged. 0.25 is adopted as the centre of that bracket, replacing an assumed 0.30 which sat high in it without a stated reason. Still a judgement within a bracket rather than a single reported figure, so the type stays assumption.</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>DO NOT substitute the national fugitives share. ECCC's 2026 executive summary reports 46 MtCO2e of oil and gas fugitive methane within roughly 66 MtCO2e of total Fugitive Sources, a share near 70%. This model's upstream stage covers production and processing in total, INCLUDING stationary combustion and flaring, which are nearly all CO2. Applying a fugitives-only share here would overstate methane by roughly a factor of two. Canada's NIR gives about 20% for the oil and gas sector nationally, but that includes oil sands, which are far more CO2-intensive than gas production. WHAT THIS VALUE DRIVES: the CO2 floor in the per-gas split (inventory_as_reported x (1 - share) = 0.165 at 0.25, was 0.154 at 0.30), and through it lifetime_co2_only_mt, lifetime_ch4_kt and the SC-CH4 damages line; and the near_term_methane_gwp20 scenario factor. It does NOT drive the measurement_central 0.25 or measurement_high 0.26 upstream factors, which are stored values on the Scenarios sheet: 0.22 x (1 - s + 1.5s) is 0.2530 at s=0.30 and 0.2475 at s=0.25, both rounding to the stored 0.25. The headline lifetime, peak and territorial split are therefore unchanged by this move. OTHER ROUTES ATTEMPTED 3 September 2026 and not closed: the ECCC National Inventory Report Part 3 provincial tables (category 1.B.2 for British Columbia) exist but are served through a JavaScript data-mart portal rather than a direct download; the UNFCCC Common Reporting Tables for Canada are the route that would work. The BC Provincial Inventory methodology report confirms upstream fugitives are Tier 3 bottom-up facility by facility, so the underlying data distinguishes gases even though the published provincial tables are CO2e only.</t>
+          <t>DO NOT substitute the national fugitives share. ECCC's 2026 executive summary reports 46 MtCO2e of oil and gas fugitive methane within roughly 66 MtCO2e of total Fugitive Sources, a share near 70%. This model's upstream stage covers production and processing in total, INCLUDING stationary combustion and flaring, which are nearly all CO2. Applying a fugitives-only share here would overstate methane by roughly a factor of two. Canada's NIR gives about 20% for the oil and gas sector nationally, but that includes oil sands, which are far more CO2-intensive than gas production. WHAT THIS VALUE DRIVES: the CO2 floor in the per-gas split (inventory_as_reported x (1 - share) = 0.1844 at 0.25 on the 0.246 base; 0.165 on the old 0.22 base, 0.154 at a share of 0.30), and through it lifetime_co2_only_mt, lifetime_ch4_kt and the SC-CH4 damages line; and the near_term_methane_gwp20 scenario factor. SINCE 3 September 2026 it DOES visibly drive the stored measurement_central and measurement_high factors, which are now stored to three decimals: 0.246 x (1 - s + 1.5s) is 0.283 at s=0.30 and 0.277 at s=0.25. Under the previous two-decimal storage both rounded to 0.25 and the headline was insensitive to the share; that insensitivity was a rounding artefact, not a property of the model. OTHER ROUTES ATTEMPTED 3 September 2026 and not closed: the ECCC National Inventory Report Part 3 provincial tables (category 1.B.2 for British Columbia) exist but are served through a JavaScript data-mart portal rather than a direct download; the UNFCCC Common Reporting Tables for Canada are the route that would work. The BC Provincial Inventory methodology report confirms upstream fugitives are Tier 3 bottom-up facility by facility, so the underlying data distinguishes gases even though the published provincial tables are CO2e only.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>upstream 0.22</t>
+          <t>upstream 0.246</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Lower bound</t>
+          <t>Lower bound. Was 0.22 until 3 September 2026 (netted the retired pipeline 0.10); 0.246 nets the current 0.074. Derivation in the Emission Factors basis cell.</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>upstream 0.25</t>
+          <t>upstream 0.277</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5104,7 +5104,11 @@
           <t>Default. Three independent measurement studies agree on 1.5x</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Was 0.25 (0.2475 at two decimals) until 3 September 2026. = 0.246 x (1 - 0.25 + 1.5 x 0.25).</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5114,7 +5118,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>upstream 0.26</t>
+          <t>upstream 0.289</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -5132,7 +5136,11 @@
           <t>BC aircraft survey finds 1.7x</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Was 0.26 until 3 September 2026. = 0.246 x (1 - 0.25 + 1.7 x 0.25).</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5142,7 +5150,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>upstream 0.393</t>
+          <t>upstream 0.44</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5157,12 +5165,12 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Non-methane portion of inventory_as_reported (0.22 x 0.75 = 0.165) is unchanged. Methane portion is inventory x upstream_ch4_share x upstream_measurement_correction x (gwp20_ch4 / gwp100_ch4). Depends on the methane share of 0.25. Was 0.428 at a share of 0.30, and 0.33 before that (= 0.22 x 1.5 on the whole factor, which treated all upstream as methane).</t>
+          <t>Non-methane portion of inventory_as_reported (0.246 x 0.75 = 0.1844) is unchanged. Methane portion is inventory x upstream_ch4_share x upstream_measurement_correction x (gwp20_ch4 / gwp100_ch4) = 0.246 x 0.25 x 1.5 x (82.5 / 29.8) = 0.2552. Total 0.4395, stored 0.44. Was 0.393 on the 0.22 base, 0.428 at a share of 0.30, and 0.33 before that (= 0.22 x 1.5 on the whole factor).</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Result 0.393 depends on upstream_ch4_share = 0.25, itself the centre of the 18-34% Johnson et al. bracket. Pipeline methane is not re-weighted: no pipeline methane share exists.</t>
+          <t>Result 0.44 depends on upstream_ch4_share = 0.25 and on the 0.246 inventory base. Pipeline methane is not re-weighted: no pipeline methane share exists.</t>
         </is>
       </c>
     </row>
@@ -5398,7 +5406,7 @@
       </c>
       <c r="O2" s="4" t="inlineStr">
         <is>
-          <t>80.1 mtpa (14.0 operating, 5.4 under construction, 60.7 proposed)</t>
+          <t>79.6 mtpa (14.0 operating, 5.4 under construction, 60.2 proposed)</t>
         </is>
       </c>
       <c r="P2" s="4" t="inlineStr">
@@ -5470,7 +5478,7 @@
       </c>
       <c r="O3" s="4" t="inlineStr">
         <is>
-          <t>0.90 mtpa (Tilbury Phase 1a and 1b)</t>
+          <t>3.40 mtpa (Tilbury Phase 1a 0.25 operating; Tilbury Phase 1b 0.65 and Tilbury Phase 2 2.50 proposed)</t>
         </is>
       </c>
       <c r="P3" s="4" t="inlineStr">
@@ -5861,7 +5869,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>max(upstream factor for the scenario - inventory_as_reported x (1 - upstream_ch4_share), 0). At measurement_central: 0.25 - 0.22 x 0.7 = 0.096.</t>
+          <t>max(upstream factor for the scenario - inventory_as_reported x (1 - upstream_ch4_share), 0). At measurement_central: 0.277 - 0.246 x 0.75 = 0.0922 (was 0.25 - 0.22 x 0.7 = 0.096 before 3 September 2026).</t>
         </is>
       </c>
     </row>
@@ -5910,7 +5918,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Methane mass behind the CH4-derived CO2e in an asset-year. Not defined for the near_term_methane_gwp20 scenario, whose upstream factor (0.22 x 1.5) is not a GWP100 CO2e figure; that scenario's cell is left blank rather than divided by the wrong GWP.</t>
+          <t>Methane mass behind the CH4-derived CO2e in an asset-year. Not defined for the near_term_methane_gwp20 scenario, whose upstream factor (GWP20-weighted methane portion) is not a GWP100 CO2e figure; that scenario's cell is left blank rather than divided by the wrong GWP.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">

--- a/Inputs/Canada_LNG_Data_Inputs.xlsx
+++ b/Inputs/Canada_LNG_Data_Inputs.xlsx
@@ -1360,12 +1360,12 @@
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>0.021 tCO2e per t LNG. Gan et al. (2024), Communications Earth &amp; Environment, https://doi.org/10.1038/s43247-024-01988-2 : peer-reviewed US LNG lifecycle assessment placing regasification at 0.021 tCO2e/t. Adopted 3 September 2026, replacing an uncited 0.04 that sat above the top of the IEA range below. The previous 0.04 was labelled RMI Oil Climate Index; no OCI+ table or page states 0.04 t/t.</t>
+          <t>0.021 tCO2e per t LNG. Mukherjee et al. (2025), Communications Earth &amp; Environment 6:16, https://doi.org/10.1038/s43247-024-01988-2 : peer-reviewed US LNG lifecycle assessment placing regasification at 0.021 tCO2e/t. Adopted 3 September 2026, replacing an uncited 0.04 that sat above the top of the IEA range below. The previous 0.04 was labelled RMI Oil Climate Index; no OCI+ table or page states 0.04 t/t.</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>IEA (2025), Assessing Emissions from LNG Supply and Abatement Options, IEA, Paris, CC BY 4.0, page 16: "Total GHG emissions from regasification are around 0.2-0.5 g CO2-eq/MJ of gas regasified." https://iea.blob.core.windows.net/assets/df9b1bed-4e16-4db8-bec5-a5fa117a9130/AssessingemissionsfromLNGsupplyandabatementoptions.pdf . Converted at the report's own stated basis of 55 MJ per kg of methane (footnote 2, page 7): 0.2 g/MJ = 0.011 and 0.5 g/MJ = 0.0275 tCO2e per tonne. IEA takes 1 t methane as 30 t CO2 on a 100-year GWP, against this model's 29.8. The Gan et al. central of 0.021 sits inside this range.</t>
+          <t>IEA (2025), Assessing Emissions from LNG Supply and Abatement Options, IEA, Paris, CC BY 4.0, page 16: "Total GHG emissions from regasification are around 0.2-0.5 g CO2-eq/MJ of gas regasified." https://iea.blob.core.windows.net/assets/df9b1bed-4e16-4db8-bec5-a5fa117a9130/AssessingemissionsfromLNGsupplyandabatementoptions.pdf . Converted at the report's own stated basis of 55 MJ per kg of methane (footnote 2, page 7): 0.2 g/MJ = 0.011 and 0.5 g/MJ = 0.0275 tCO2e per tonne. IEA takes 1 t methane as 30 t CO2 on a 100-year GWP, against this model's 29.8. The Mukherjee et al. central of 0.021 sits inside this range.</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
